--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q959"/>
+  <dimension ref="A1:Q980"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -66275,6 +66275,1455 @@
         <v>12.0</v>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B960" s="2" t="n">
+        <v>562020.0</v>
+      </c>
+      <c r="C960" s="2" t="inlineStr">
+        <is>
+          <t>08760010007</t>
+        </is>
+      </c>
+      <c r="D960" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E960" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F960" s="2" t="inlineStr">
+        <is>
+          <t>335 OLE GESTAO COMERCIAL E ADMINISTRATIVA LTDA</t>
+        </is>
+      </c>
+      <c r="G960" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H960" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I960" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J960" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K960" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L960" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M960" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N960" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O960" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P960" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q960" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B961" s="2" t="n">
+        <v>562020.0</v>
+      </c>
+      <c r="C961" s="2" t="inlineStr">
+        <is>
+          <t>08760014005</t>
+        </is>
+      </c>
+      <c r="D961" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE NUDE</t>
+        </is>
+      </c>
+      <c r="E961" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F961" s="2" t="inlineStr">
+        <is>
+          <t>335 OLE GESTAO COMERCIAL E ADMINISTRATIVA LTDA</t>
+        </is>
+      </c>
+      <c r="G961" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H961" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I961" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J961" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K961" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L961" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M961" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N961" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O961" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P961" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q961" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B962" s="2" t="n">
+        <v>562027.0</v>
+      </c>
+      <c r="C962" s="2" t="inlineStr">
+        <is>
+          <t>44860000341</t>
+        </is>
+      </c>
+      <c r="D962" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E962" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F962" s="2" t="inlineStr">
+        <is>
+          <t>273 GLAUCIANE APARECIDA BERNARDES</t>
+        </is>
+      </c>
+      <c r="G962" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H962" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I962" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J962" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K962" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L962" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M962" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N962" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O962" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P962" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q962" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B963" s="2" t="n">
+        <v>562027.0</v>
+      </c>
+      <c r="C963" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D963" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E963" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F963" s="2" t="inlineStr">
+        <is>
+          <t>273 GLAUCIANE APARECIDA BERNARDES</t>
+        </is>
+      </c>
+      <c r="G963" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H963" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I963" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J963" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K963" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L963" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M963" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N963" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O963" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P963" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q963" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B964" s="2" t="n">
+        <v>562036.0</v>
+      </c>
+      <c r="C964" s="2" t="inlineStr">
+        <is>
+          <t>08760000007</t>
+        </is>
+      </c>
+      <c r="D964" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E964" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F964" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G964" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H964" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I964" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J964" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K964" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L964" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M964" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N964" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O964" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P964" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q964" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B965" s="2" t="n">
+        <v>562036.0</v>
+      </c>
+      <c r="C965" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D965" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E965" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F965" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G965" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H965" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I965" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J965" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K965" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L965" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M965" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N965" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O965" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P965" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q965" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B966" s="2" t="n">
+        <v>562036.0</v>
+      </c>
+      <c r="C966" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D966" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E966" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F966" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G966" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H966" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I966" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J966" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K966" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L966" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M966" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N966" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O966" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P966" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q966" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B967" s="2" t="n">
+        <v>562037.0</v>
+      </c>
+      <c r="C967" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D967" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E967" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F967" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G967" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I967" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J967" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K967" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L967" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M967" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N967" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O967" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P967" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q967" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B968" s="2" t="n">
+        <v>562037.0</v>
+      </c>
+      <c r="C968" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D968" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E968" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F968" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G968" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H968" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I968" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J968" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K968" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L968" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M968" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N968" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O968" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P968" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q968" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B969" s="2" t="n">
+        <v>562050.0</v>
+      </c>
+      <c r="C969" s="2" t="inlineStr">
+        <is>
+          <t>08760010007</t>
+        </is>
+      </c>
+      <c r="D969" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E969" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F969" s="2" t="inlineStr">
+        <is>
+          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G969" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H969" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I969" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J969" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K969" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L969" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M969" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N969" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O969" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P969" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q969" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B970" s="2" t="n">
+        <v>562050.0</v>
+      </c>
+      <c r="C970" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D970" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E970" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F970" s="2" t="inlineStr">
+        <is>
+          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G970" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H970" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I970" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J970" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K970" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L970" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M970" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N970" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O970" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P970" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q970" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B971" s="2" t="n">
+        <v>562051.0</v>
+      </c>
+      <c r="C971" s="2" t="inlineStr">
+        <is>
+          <t>43860010411</t>
+        </is>
+      </c>
+      <c r="D971" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E971" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F971" s="2" t="inlineStr">
+        <is>
+          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G971" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H971" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I971" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J971" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K971" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L971" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M971" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N971" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O971" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P971" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q971" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B972" s="2" t="n">
+        <v>562073.0</v>
+      </c>
+      <c r="C972" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D972" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E972" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F972" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G972" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H972" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I972" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J972" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K972" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L972" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M972" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N972" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="O972" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P972" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q972" s="2" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B973" s="2" t="n">
+        <v>562073.0</v>
+      </c>
+      <c r="C973" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D973" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E973" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F973" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G973" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H973" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I973" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J973" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K973" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L973" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M973" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N973" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O973" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P973" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q973" s="2" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B974" s="2" t="n">
+        <v>562074.0</v>
+      </c>
+      <c r="C974" s="2" t="inlineStr">
+        <is>
+          <t>45560000017</t>
+        </is>
+      </c>
+      <c r="D974" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E974" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F974" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G974" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H974" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I974" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J974" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K974" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L974" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M974" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N974" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O974" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="P974" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q974" s="2" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B975" s="2" t="n">
+        <v>562075.0</v>
+      </c>
+      <c r="C975" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D975" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E975" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F975" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G975" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H975" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I975" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J975" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K975" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L975" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M975" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N975" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O975" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P975" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q975" s="2" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B976" s="2" t="n">
+        <v>562862.0</v>
+      </c>
+      <c r="C976" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D976" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E976" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F976" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G976" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H976" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I976" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J976" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K976" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L976" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M976" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N976" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O976" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P976" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q976" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B977" s="2" t="n">
+        <v>562863.0</v>
+      </c>
+      <c r="C977" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D977" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E977" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F977" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G977" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H977" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I977" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J977" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K977" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L977" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M977" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N977" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O977" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P977" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q977" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B978" s="2" t="n">
+        <v>562863.0</v>
+      </c>
+      <c r="C978" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D978" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E978" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F978" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G978" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H978" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I978" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J978" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K978" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L978" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M978" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N978" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O978" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P978" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q978" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B979" s="2" t="n">
+        <v>562864.0</v>
+      </c>
+      <c r="C979" s="2" t="inlineStr">
+        <is>
+          <t>43860000017</t>
+        </is>
+      </c>
+      <c r="D979" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E979" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F979" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G979" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H979" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I979" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J979" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K979" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="L979" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M979" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N979" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O979" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P979" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q979" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B980" s="2" t="n">
+        <v>562864.0</v>
+      </c>
+      <c r="C980" s="2" t="inlineStr">
+        <is>
+          <t>43860010411</t>
+        </is>
+      </c>
+      <c r="D980" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E980" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F980" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G980" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H980" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I980" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J980" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K980" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L980" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M980" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N980" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O980" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P980" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q980" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q980"/>
+  <dimension ref="A1:Q1023"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -67722,6 +67722,2973 @@
       </c>
       <c r="Q980" s="2" t="n">
         <v>12.0</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B981" s="2" t="n">
+        <v>562875.0</v>
+      </c>
+      <c r="C981" s="2" t="inlineStr">
+        <is>
+          <t>44860000411</t>
+        </is>
+      </c>
+      <c r="D981" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E981" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F981" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G981" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H981" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I981" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J981" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K981" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L981" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M981" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N981" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O981" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P981" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q981" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B982" s="2" t="n">
+        <v>562875.0</v>
+      </c>
+      <c r="C982" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D982" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E982" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F982" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G982" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H982" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I982" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J982" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K982" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L982" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M982" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N982" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O982" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P982" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q982" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B983" s="2" t="n">
+        <v>562876.0</v>
+      </c>
+      <c r="C983" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D983" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E983" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F983" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G983" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H983" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I983" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J983" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K983" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L983" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M983" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N983" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O983" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P983" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q983" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B984" s="2" t="n">
+        <v>562927.0</v>
+      </c>
+      <c r="C984" s="2" t="inlineStr">
+        <is>
+          <t>44860000341</t>
+        </is>
+      </c>
+      <c r="D984" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E984" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F984" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G984" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H984" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I984" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J984" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K984" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L984" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M984" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N984" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O984" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P984" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q984" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B985" s="2" t="n">
+        <v>562927.0</v>
+      </c>
+      <c r="C985" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D985" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E985" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F985" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G985" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H985" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I985" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J985" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K985" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L985" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M985" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N985" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O985" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P985" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q985" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B986" s="2" t="n">
+        <v>562927.0</v>
+      </c>
+      <c r="C986" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D986" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E986" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F986" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G986" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H986" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I986" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J986" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K986" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L986" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M986" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N986" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O986" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P986" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q986" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B987" s="2" t="n">
+        <v>562964.0</v>
+      </c>
+      <c r="C987" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D987" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E987" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F987" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G987" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H987" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I987" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J987" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K987" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L987" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M987" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N987" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O987" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P987" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q987" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B988" s="2" t="n">
+        <v>562965.0</v>
+      </c>
+      <c r="C988" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D988" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E988" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F988" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G988" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H988" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I988" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J988" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K988" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L988" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M988" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N988" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="O988" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P988" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q988" s="2" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B989" s="2" t="n">
+        <v>563038.0</v>
+      </c>
+      <c r="C989" s="2" t="inlineStr">
+        <is>
+          <t>08760020008</t>
+        </is>
+      </c>
+      <c r="D989" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE ROSA</t>
+        </is>
+      </c>
+      <c r="E989" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F989" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G989" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H989" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I989" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J989" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K989" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L989" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M989" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N989" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O989" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P989" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q989" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B990" s="2" t="n">
+        <v>563039.0</v>
+      </c>
+      <c r="C990" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D990" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E990" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F990" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G990" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H990" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I990" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J990" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K990" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L990" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M990" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N990" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O990" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P990" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q990" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B991" s="2" t="n">
+        <v>563039.0</v>
+      </c>
+      <c r="C991" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D991" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E991" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F991" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G991" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H991" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I991" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J991" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K991" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L991" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M991" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N991" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O991" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P991" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q991" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B992" s="2" t="n">
+        <v>563040.0</v>
+      </c>
+      <c r="C992" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D992" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E992" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F992" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G992" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H992" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I992" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J992" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K992" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L992" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M992" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N992" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O992" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P992" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q992" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B993" s="2" t="n">
+        <v>563041.0</v>
+      </c>
+      <c r="C993" s="2" t="inlineStr">
+        <is>
+          <t>08760020008</t>
+        </is>
+      </c>
+      <c r="D993" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE ROSA</t>
+        </is>
+      </c>
+      <c r="E993" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F993" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G993" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H993" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I993" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J993" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K993" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L993" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M993" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N993" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O993" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P993" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q993" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B994" s="2" t="n">
+        <v>563042.0</v>
+      </c>
+      <c r="C994" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D994" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E994" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F994" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G994" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H994" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I994" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J994" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K994" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L994" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M994" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N994" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O994" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P994" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q994" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B995" s="2" t="n">
+        <v>563042.0</v>
+      </c>
+      <c r="C995" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D995" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E995" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F995" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G995" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H995" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I995" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J995" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K995" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L995" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M995" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N995" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O995" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P995" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q995" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B996" s="2" t="n">
+        <v>563043.0</v>
+      </c>
+      <c r="C996" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D996" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E996" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F996" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G996" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H996" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I996" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J996" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K996" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L996" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M996" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N996" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O996" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P996" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q996" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B997" s="2" t="n">
+        <v>563044.0</v>
+      </c>
+      <c r="C997" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D997" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E997" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F997" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G997" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H997" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I997" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J997" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K997" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L997" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M997" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N997" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O997" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P997" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q997" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B998" s="2" t="n">
+        <v>563044.0</v>
+      </c>
+      <c r="C998" s="2" t="inlineStr">
+        <is>
+          <t>44860014005</t>
+        </is>
+      </c>
+      <c r="D998" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E998" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F998" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G998" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H998" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I998" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J998" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K998" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L998" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M998" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N998" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O998" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P998" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q998" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B999" s="2" t="n">
+        <v>563045.0</v>
+      </c>
+      <c r="C999" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D999" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E999" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F999" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G999" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H999" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I999" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J999" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K999" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L999" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M999" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N999" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O999" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P999" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q999" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1000" s="2" t="n">
+        <v>563046.0</v>
+      </c>
+      <c r="C1000" s="2" t="inlineStr">
+        <is>
+          <t>08760020007</t>
+        </is>
+      </c>
+      <c r="D1000" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1000" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1000" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1000" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1000" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1000" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1000" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1000" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1000" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1000" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1000" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1000" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1000" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1000" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1001" s="2" t="n">
+        <v>563047.0</v>
+      </c>
+      <c r="C1001" s="2" t="inlineStr">
+        <is>
+          <t>08760020008</t>
+        </is>
+      </c>
+      <c r="D1001" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE ROSA</t>
+        </is>
+      </c>
+      <c r="E1001" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1001" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1001" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1001" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1001" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1001" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1001" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1001" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1001" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1001" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1001" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1001" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1001" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1002" s="2" t="n">
+        <v>563048.0</v>
+      </c>
+      <c r="C1002" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1002" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1002" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1002" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1002" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1002" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1002" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1002" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1002" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1002" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1002" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1002" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1002" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1002" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1002" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1003" s="2" t="n">
+        <v>563048.0</v>
+      </c>
+      <c r="C1003" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1003" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1003" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1003" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1003" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1003" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1003" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1003" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1003" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1003" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1003" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1003" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1003" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1003" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1003" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1004" s="2" t="n">
+        <v>563049.0</v>
+      </c>
+      <c r="C1004" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D1004" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1004" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1004" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1004" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1004" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1004" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1004" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1004" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1004" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1004" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1004" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1004" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1004" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1004" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1005" s="2" t="n">
+        <v>563080.0</v>
+      </c>
+      <c r="C1005" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1005" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1005" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1005" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1005" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1005" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1005" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1005" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1005" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1005" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1005" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1005" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1005" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1005" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1005" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1006" s="2" t="n">
+        <v>563080.0</v>
+      </c>
+      <c r="C1006" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1006" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1006" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1006" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1006" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1006" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1006" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1006" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1006" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1006" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1006" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1006" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1006" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1006" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1006" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1007" s="2" t="n">
+        <v>563081.0</v>
+      </c>
+      <c r="C1007" s="2" t="inlineStr">
+        <is>
+          <t>43860010411</t>
+        </is>
+      </c>
+      <c r="D1007" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1007" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1007" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1007" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1007" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1007" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1007" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1007" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1007" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1007" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1007" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1007" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1007" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1007" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1008" s="2" t="n">
+        <v>563082.0</v>
+      </c>
+      <c r="C1008" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1008" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1008" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1008" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1008" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1008" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1008" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1008" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1008" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1008" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1008" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1008" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1008" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1008" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1008" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1009" s="2" t="n">
+        <v>563118.0</v>
+      </c>
+      <c r="C1009" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1009" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1009" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1009" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1009" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1009" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1009" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1009" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1009" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1009" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1009" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1009" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1009" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1009" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1009" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1010" s="2" t="n">
+        <v>563118.0</v>
+      </c>
+      <c r="C1010" s="2" t="inlineStr">
+        <is>
+          <t>44860000341</t>
+        </is>
+      </c>
+      <c r="D1010" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1010" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1010" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1010" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1010" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1010" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1010" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1010" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1010" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1010" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1010" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1010" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1010" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1010" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1011" s="2" t="n">
+        <v>563118.0</v>
+      </c>
+      <c r="C1011" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1011" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1011" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1011" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1011" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1011" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1011" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1011" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1011" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1011" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1011" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1011" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1011" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1011" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1011" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1012" s="2" t="n">
+        <v>563118.0</v>
+      </c>
+      <c r="C1012" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1012" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1012" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1012" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1012" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1012" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1012" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1012" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1012" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1012" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1012" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1012" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1012" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1012" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1012" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1013" s="2" t="n">
+        <v>563119.0</v>
+      </c>
+      <c r="C1013" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1013" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1013" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1013" s="2" t="inlineStr">
+        <is>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1013" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1013" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1013" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1013" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1013" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1013" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1013" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1013" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1013" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1013" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1013" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1014" s="2" t="n">
+        <v>563150.0</v>
+      </c>
+      <c r="C1014" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1014" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1014" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1014" s="2" t="inlineStr">
+        <is>
+          <t>301 JRM VELOSO REPRESENTAÇÕES DE CALÇADOS LTDA</t>
+        </is>
+      </c>
+      <c r="G1014" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1014" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1014" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1014" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1014" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1014" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1014" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1014" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1014" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1014" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1014" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1015" s="2" t="n">
+        <v>563150.0</v>
+      </c>
+      <c r="C1015" s="2" t="inlineStr">
+        <is>
+          <t>08760020007</t>
+        </is>
+      </c>
+      <c r="D1015" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1015" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1015" s="2" t="inlineStr">
+        <is>
+          <t>301 JRM VELOSO REPRESENTAÇÕES DE CALÇADOS LTDA</t>
+        </is>
+      </c>
+      <c r="G1015" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1015" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1015" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1015" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1015" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1015" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1015" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1015" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1015" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1015" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1015" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1016" s="2" t="n">
+        <v>563151.0</v>
+      </c>
+      <c r="C1016" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1016" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1016" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1016" s="2" t="inlineStr">
+        <is>
+          <t>301 JRM VELOSO REPRESENTAÇÕES DE CALÇADOS LTDA</t>
+        </is>
+      </c>
+      <c r="G1016" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1016" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1016" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1016" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1016" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1016" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1016" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1016" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1016" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1016" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1016" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1017" s="2" t="n">
+        <v>563151.0</v>
+      </c>
+      <c r="C1017" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1017" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1017" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1017" s="2" t="inlineStr">
+        <is>
+          <t>301 JRM VELOSO REPRESENTAÇÕES DE CALÇADOS LTDA</t>
+        </is>
+      </c>
+      <c r="G1017" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1017" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1017" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1017" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1017" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1017" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1017" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1017" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1017" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1017" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1017" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1018" s="2" t="n">
+        <v>563224.0</v>
+      </c>
+      <c r="C1018" s="2" t="inlineStr">
+        <is>
+          <t>45560000007</t>
+        </is>
+      </c>
+      <c r="D1018" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO PRETO</t>
+        </is>
+      </c>
+      <c r="E1018" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1018" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1018" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1018" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1018" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1018" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1018" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1018" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1018" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1018" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1018" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1018" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1018" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1019" s="2" t="n">
+        <v>563224.0</v>
+      </c>
+      <c r="C1019" s="2" t="inlineStr">
+        <is>
+          <t>45560003330</t>
+        </is>
+      </c>
+      <c r="D1019" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO MARFIM/OURO</t>
+        </is>
+      </c>
+      <c r="E1019" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1019" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1019" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1019" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1019" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1019" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1019" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1019" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1019" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1019" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1019" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1019" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1019" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1020" s="2" t="n">
+        <v>563225.0</v>
+      </c>
+      <c r="C1020" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1020" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1020" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1020" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1020" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1020" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1020" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1020" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1020" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1020" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1020" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1020" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1020" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1020" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1020" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1021" s="2" t="n">
+        <v>563225.0</v>
+      </c>
+      <c r="C1021" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1021" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1021" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1021" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1021" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1021" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1021" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1021" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1021" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1021" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1021" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1021" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1021" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1021" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1021" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="B1022" s="2" t="n">
+        <v>563226.0</v>
+      </c>
+      <c r="C1022" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1022" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1022" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1022" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1022" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1022" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1022" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1022" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1022" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1022" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1022" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1022" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1022" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1022" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1022" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1023" s="2" t="n">
+        <v>563251.0</v>
+      </c>
+      <c r="C1023" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1023" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1023" s="2" t="inlineStr">
+        <is>
+          <t>MS/MT</t>
+        </is>
+      </c>
+      <c r="F1023" s="2" t="inlineStr">
+        <is>
+          <t>266 LORAN DA SILVA SANTOS REPRESENTAÇÕES EIRELI</t>
+        </is>
+      </c>
+      <c r="G1023" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1023" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1023" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1023" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1023" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1023" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1023" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1023" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1023" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1023" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1023" s="2" t="n">
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>

--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q1023"/>
+  <dimension ref="A1:Q1072"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -70689,6 +70689,3387 @@
       </c>
       <c r="Q1023" s="2" t="n">
         <v>9.0</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1024" s="2" t="n">
+        <v>563274.0</v>
+      </c>
+      <c r="C1024" s="2" t="inlineStr">
+        <is>
+          <t>43860010411</t>
+        </is>
+      </c>
+      <c r="D1024" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1024" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1024" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1024" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1024" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1024" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1024" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1024" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1024" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1024" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1024" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1024" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1024" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1024" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1025" s="2" t="n">
+        <v>563275.0</v>
+      </c>
+      <c r="C1025" s="2" t="inlineStr">
+        <is>
+          <t>44860000411</t>
+        </is>
+      </c>
+      <c r="D1025" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1025" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1025" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1025" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1025" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1025" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1025" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1025" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1025" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1025" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1025" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1025" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1025" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1025" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1026" s="2" t="n">
+        <v>563275.0</v>
+      </c>
+      <c r="C1026" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1026" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1026" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1026" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1026" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1026" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1026" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1026" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1026" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1026" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1026" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1026" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1026" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1026" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1026" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1027" s="2" t="n">
+        <v>563285.0</v>
+      </c>
+      <c r="C1027" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1027" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1027" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1027" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1027" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1027" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1027" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1027" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="K1027" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="L1027" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="M1027" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="N1027" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O1027" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1027" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1027" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1028" s="2" t="n">
+        <v>563286.0</v>
+      </c>
+      <c r="C1028" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1028" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1028" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1028" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1028" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1028" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1028" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1028" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1028" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1028" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1028" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1028" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1028" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1028" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1028" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1029" s="2" t="n">
+        <v>563288.0</v>
+      </c>
+      <c r="C1029" s="2" t="inlineStr">
+        <is>
+          <t>08760000017</t>
+        </is>
+      </c>
+      <c r="D1029" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1029" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1029" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1029" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1029" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1029" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1029" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1029" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="L1029" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="M1029" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="N1029" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O1029" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="P1029" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1029" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1030" s="2" t="n">
+        <v>563288.0</v>
+      </c>
+      <c r="C1030" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1030" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1030" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1030" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1030" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1030" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1030" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1030" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1030" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1030" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1030" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1030" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1030" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1030" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1030" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1031" s="2" t="n">
+        <v>563288.0</v>
+      </c>
+      <c r="C1031" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1031" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1031" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1031" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1031" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1031" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1031" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1031" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1031" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1031" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1031" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1031" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1031" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1031" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1031" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1032" s="2" t="n">
+        <v>563289.0</v>
+      </c>
+      <c r="C1032" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1032" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1032" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1032" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1032" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1032" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1032" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1032" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1032" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1032" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1032" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1032" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1032" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1032" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1032" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1033" s="2" t="n">
+        <v>563291.0</v>
+      </c>
+      <c r="C1033" s="2" t="inlineStr">
+        <is>
+          <t>44860000411</t>
+        </is>
+      </c>
+      <c r="D1033" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1033" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1033" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1033" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1033" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1033" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1033" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1033" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1033" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1033" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1033" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1033" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1033" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1033" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1034" s="2" t="n">
+        <v>563292.0</v>
+      </c>
+      <c r="C1034" s="2" t="inlineStr">
+        <is>
+          <t>08760000017</t>
+        </is>
+      </c>
+      <c r="D1034" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1034" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1034" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1034" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1034" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1034" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1034" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1034" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1034" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1034" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1034" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1034" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1034" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1034" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1035" s="2" t="n">
+        <v>563292.0</v>
+      </c>
+      <c r="C1035" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1035" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1035" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1035" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1035" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1035" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1035" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1035" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1035" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1035" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1035" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1035" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1035" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1035" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1035" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1036" s="2" t="n">
+        <v>563292.0</v>
+      </c>
+      <c r="C1036" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1036" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1036" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1036" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1036" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1036" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1036" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1036" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1036" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1036" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1036" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1036" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1036" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1036" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1036" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1037" s="2" t="n">
+        <v>563335.0</v>
+      </c>
+      <c r="C1037" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1037" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1037" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1037" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1037" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1037" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1037" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1037" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1037" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1037" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1037" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1037" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1037" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1037" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1037" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1038" s="2" t="n">
+        <v>563336.0</v>
+      </c>
+      <c r="C1038" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1038" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1038" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1038" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1038" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1038" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1038" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1038" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1038" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1038" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1038" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1038" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1038" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1038" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1038" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1039" s="2" t="n">
+        <v>563337.0</v>
+      </c>
+      <c r="C1039" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1039" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1039" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1039" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1039" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1039" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1039" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1039" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1039" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1039" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1039" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1039" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1039" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1039" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1039" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1040" s="2" t="n">
+        <v>563337.0</v>
+      </c>
+      <c r="C1040" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1040" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1040" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1040" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1040" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1040" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1040" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1040" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1040" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1040" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1040" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1040" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1040" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1040" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1040" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1041" s="2" t="n">
+        <v>563337.0</v>
+      </c>
+      <c r="C1041" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1041" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1041" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1041" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1041" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1041" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1041" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1041" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1041" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1041" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1041" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1041" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1041" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1041" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1041" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1042" s="2" t="n">
+        <v>563350.0</v>
+      </c>
+      <c r="C1042" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1042" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1042" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1042" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1042" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1042" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1042" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1042" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1042" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1042" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1042" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1042" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1042" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1042" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1042" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1043" s="2" t="n">
+        <v>563351.0</v>
+      </c>
+      <c r="C1043" s="2" t="inlineStr">
+        <is>
+          <t>44860014005</t>
+        </is>
+      </c>
+      <c r="D1043" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1043" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1043" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1043" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1043" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1043" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1043" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1043" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1043" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1043" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1043" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1043" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1043" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1043" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1044" s="2" t="n">
+        <v>563352.0</v>
+      </c>
+      <c r="C1044" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1044" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1044" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1044" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1044" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1044" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1044" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1044" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1044" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1044" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1044" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1044" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1044" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1044" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1044" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1045" s="2" t="n">
+        <v>563352.0</v>
+      </c>
+      <c r="C1045" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1045" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1045" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1045" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1045" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1045" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1045" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1045" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1045" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1045" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1045" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1045" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1045" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1045" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1045" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1046" s="2" t="n">
+        <v>563390.0</v>
+      </c>
+      <c r="C1046" s="2" t="inlineStr">
+        <is>
+          <t>08760000007</t>
+        </is>
+      </c>
+      <c r="D1046" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1046" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1046" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1046" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1046" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1046" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1046" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1046" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1046" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1046" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1046" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1046" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1046" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1046" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1047" s="2" t="n">
+        <v>563390.0</v>
+      </c>
+      <c r="C1047" s="2" t="inlineStr">
+        <is>
+          <t>08760004005</t>
+        </is>
+      </c>
+      <c r="D1047" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE NUDE</t>
+        </is>
+      </c>
+      <c r="E1047" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1047" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1047" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1047" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1047" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1047" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1047" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1047" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1047" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1047" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1047" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1047" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1047" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1048" s="2" t="n">
+        <v>563391.0</v>
+      </c>
+      <c r="C1048" s="2" t="inlineStr">
+        <is>
+          <t>43860000017</t>
+        </is>
+      </c>
+      <c r="D1048" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1048" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1048" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1048" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1048" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1048" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1048" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1048" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1048" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1048" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1048" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1048" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1048" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1048" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1049" s="2" t="n">
+        <v>563391.0</v>
+      </c>
+      <c r="C1049" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D1049" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1049" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1049" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1049" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1049" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1049" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1049" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1049" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1049" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1049" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1049" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1049" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1049" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1049" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1050" s="2" t="n">
+        <v>563392.0</v>
+      </c>
+      <c r="C1050" s="2" t="inlineStr">
+        <is>
+          <t>45560000017</t>
+        </is>
+      </c>
+      <c r="D1050" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1050" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1050" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1050" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1050" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1050" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1050" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1050" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1050" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1050" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1050" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1050" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1050" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1050" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1051" s="2" t="n">
+        <v>563392.0</v>
+      </c>
+      <c r="C1051" s="2" t="inlineStr">
+        <is>
+          <t>45560003330</t>
+        </is>
+      </c>
+      <c r="D1051" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO MARFIM/OURO</t>
+        </is>
+      </c>
+      <c r="E1051" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1051" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1051" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1051" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1051" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1051" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1051" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1051" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1051" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1051" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1051" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1051" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1051" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1052" s="2" t="n">
+        <v>563454.0</v>
+      </c>
+      <c r="C1052" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1052" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1052" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F1052" s="2" t="inlineStr">
+        <is>
+          <t>296 ANA PAULA CATELAN DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="G1052" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1052" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1052" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1052" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1052" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1052" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1052" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1052" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1052" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1052" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1052" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1053" s="2" t="n">
+        <v>563475.0</v>
+      </c>
+      <c r="C1053" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1053" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1053" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1053" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1053" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1053" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1053" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1053" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1053" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1053" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1053" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1053" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1053" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="P1053" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1053" s="2" t="n">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1054" s="2" t="n">
+        <v>563475.0</v>
+      </c>
+      <c r="C1054" s="2" t="inlineStr">
+        <is>
+          <t>44860014005</t>
+        </is>
+      </c>
+      <c r="D1054" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1054" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1054" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1054" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1054" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1054" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1054" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1054" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1054" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1054" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1054" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1054" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1054" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1054" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1055" s="2" t="n">
+        <v>563482.0</v>
+      </c>
+      <c r="C1055" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1055" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1055" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1055" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1055" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1055" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1055" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1055" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1055" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1055" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1055" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1055" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1055" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1055" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1055" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1056" s="2" t="n">
+        <v>563482.0</v>
+      </c>
+      <c r="C1056" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1056" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1056" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1056" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1056" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1056" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1056" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1056" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1056" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1056" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1056" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1056" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1056" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1056" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1056" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1057" s="2" t="n">
+        <v>563483.0</v>
+      </c>
+      <c r="C1057" s="2" t="inlineStr">
+        <is>
+          <t>08760010007</t>
+        </is>
+      </c>
+      <c r="D1057" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1057" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1057" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1057" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1057" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1057" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1057" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1057" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1057" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1057" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1057" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1057" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1057" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1057" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1058" s="2" t="n">
+        <v>563483.0</v>
+      </c>
+      <c r="C1058" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1058" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1058" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1058" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1058" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1058" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1058" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1058" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1058" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1058" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1058" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1058" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1058" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1058" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1058" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1059" s="2" t="n">
+        <v>563490.0</v>
+      </c>
+      <c r="C1059" s="2" t="inlineStr">
+        <is>
+          <t>08760020007</t>
+        </is>
+      </c>
+      <c r="D1059" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1059" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F1059" s="2" t="inlineStr">
+        <is>
+          <t>327 BOLA REPRESENTACOES COMERCIAIS</t>
+        </is>
+      </c>
+      <c r="G1059" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1059" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1059" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1059" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1059" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1059" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1059" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1059" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1059" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1059" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1059" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1060" s="2" t="n">
+        <v>563491.0</v>
+      </c>
+      <c r="C1060" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1060" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1060" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F1060" s="2" t="inlineStr">
+        <is>
+          <t>327 BOLA REPRESENTACOES COMERCIAIS</t>
+        </is>
+      </c>
+      <c r="G1060" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1060" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1060" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1060" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1060" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1060" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1060" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1060" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1060" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1060" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1060" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1061" s="2" t="n">
+        <v>563523.0</v>
+      </c>
+      <c r="C1061" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1061" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1061" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1061" s="2" t="inlineStr">
+        <is>
+          <t>282 NRIZZO REPRESENTACOES PROMOCOES E INTERMEDIACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1061" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1061" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1061" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1061" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="K1061" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="L1061" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="M1061" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="N1061" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="O1061" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="P1061" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="Q1061" s="2" t="n">
+        <v>36.0</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1062" s="2" t="n">
+        <v>563523.0</v>
+      </c>
+      <c r="C1062" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1062" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1062" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1062" s="2" t="inlineStr">
+        <is>
+          <t>282 NRIZZO REPRESENTACOES PROMOCOES E INTERMEDIACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1062" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1062" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1062" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1062" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K1062" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="L1062" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="M1062" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="N1062" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="O1062" s="2" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="P1062" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="Q1062" s="2" t="n">
+        <v>36.0</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1063" s="2" t="n">
+        <v>563556.0</v>
+      </c>
+      <c r="C1063" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1063" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1063" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1063" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1063" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1063" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1063" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1063" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1063" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1063" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1063" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1063" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1063" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1063" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1063" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1064" s="2" t="n">
+        <v>563556.0</v>
+      </c>
+      <c r="C1064" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1064" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1064" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1064" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1064" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1064" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1064" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1064" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1064" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1064" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1064" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1064" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1064" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1064" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1064" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1065" s="2" t="n">
+        <v>563557.0</v>
+      </c>
+      <c r="C1065" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1065" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1065" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1065" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1065" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1065" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1065" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1065" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1065" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1065" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1065" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1065" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1065" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1065" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1065" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1066" s="2" t="n">
+        <v>563574.0</v>
+      </c>
+      <c r="C1066" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1066" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1066" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1066" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1066" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1066" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1066" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1066" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1066" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1066" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1066" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1066" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1066" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1066" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1066" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1067" s="2" t="n">
+        <v>563574.0</v>
+      </c>
+      <c r="C1067" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1067" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1067" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1067" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1067" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1067" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1067" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1067" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1067" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1067" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1067" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1067" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1067" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1067" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1067" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1068" s="2" t="n">
+        <v>563587.0</v>
+      </c>
+      <c r="C1068" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1068" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1068" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1068" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1068" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1068" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1068" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1068" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1068" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1068" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1068" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1068" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1068" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1068" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1068" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1069" s="2" t="n">
+        <v>563587.0</v>
+      </c>
+      <c r="C1069" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1069" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1069" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1069" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1069" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1069" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1069" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1069" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1069" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1069" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1069" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1069" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1069" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1069" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1069" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1070" s="2" t="n">
+        <v>563588.0</v>
+      </c>
+      <c r="C1070" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1070" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1070" s="2" t="inlineStr">
+        <is>
+          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1070" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1070" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1070" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1070" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1070" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1070" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1070" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1070" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1070" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1070" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1070" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1070" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1071" s="2" t="n">
+        <v>563628.0</v>
+      </c>
+      <c r="C1071" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1071" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1071" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1071" s="2" t="inlineStr">
+        <is>
+          <t>369 CARVALHO NUNES REPRESENTACAO COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1071" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1071" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1071" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1071" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1071" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1071" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1071" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1071" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1071" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1071" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1071" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="B1072" s="2" t="n">
+        <v>563628.0</v>
+      </c>
+      <c r="C1072" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1072" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1072" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1072" s="2" t="inlineStr">
+        <is>
+          <t>369 CARVALHO NUNES REPRESENTACAO COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1072" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1072" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1072" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1072" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1072" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1072" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1072" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1072" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1072" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1072" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1072" s="2" t="n">
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>

--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -13580,7 +13580,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
@@ -14270,7 +14270,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -19721,7 +19721,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -21101,7 +21101,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
@@ -21446,7 +21446,7 @@
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
@@ -21515,7 +21515,7 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr">
@@ -21653,7 +21653,7 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
@@ -21998,7 +21998,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
@@ -22619,7 +22619,7 @@
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr">
@@ -22895,7 +22895,7 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
@@ -22964,7 +22964,7 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
@@ -23309,7 +23309,7 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
@@ -23378,7 +23378,7 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
@@ -23723,7 +23723,7 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
@@ -23861,7 +23861,7 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
@@ -24137,7 +24137,7 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
@@ -24418,7 +24418,7 @@
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
@@ -24487,7 +24487,7 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G355" s="2" t="inlineStr">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G356" s="2" t="inlineStr">
@@ -25034,7 +25034,7 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
@@ -25103,7 +25103,7 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr">
@@ -25172,7 +25172,7 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
@@ -25862,7 +25862,7 @@
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
@@ -26069,7 +26069,7 @@
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
@@ -26138,7 +26138,7 @@
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
@@ -26207,7 +26207,7 @@
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
@@ -26276,7 +26276,7 @@
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
@@ -26345,7 +26345,7 @@
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
@@ -26483,7 +26483,7 @@
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -26552,7 +26552,7 @@
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -26621,7 +26621,7 @@
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
@@ -30347,7 +30347,7 @@
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
@@ -30416,7 +30416,7 @@
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr">
@@ -30485,7 +30485,7 @@
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
@@ -31796,7 +31796,7 @@
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
@@ -32003,7 +32003,7 @@
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr">
@@ -32072,7 +32072,7 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -32141,7 +32141,7 @@
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -32210,7 +32210,7 @@
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr">
@@ -32279,7 +32279,7 @@
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr">
@@ -32348,7 +32348,7 @@
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr">
@@ -32417,7 +32417,7 @@
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr">
@@ -37799,7 +37799,7 @@
       </c>
       <c r="E547" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F547" s="2" t="inlineStr">
@@ -37868,7 +37868,7 @@
       </c>
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F548" s="2" t="inlineStr">
@@ -37937,7 +37937,7 @@
       </c>
       <c r="E549" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F549" s="2" t="inlineStr">
@@ -38006,7 +38006,7 @@
       </c>
       <c r="E550" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F550" s="2" t="inlineStr">
@@ -38075,7 +38075,7 @@
       </c>
       <c r="E551" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F551" s="2" t="inlineStr">
@@ -38144,7 +38144,7 @@
       </c>
       <c r="E552" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F552" s="2" t="inlineStr">
@@ -38213,7 +38213,7 @@
       </c>
       <c r="E553" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F553" s="2" t="inlineStr">
@@ -38282,7 +38282,7 @@
       </c>
       <c r="E554" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F554" s="2" t="inlineStr">
@@ -38351,7 +38351,7 @@
       </c>
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F555" s="2" t="inlineStr">
@@ -38420,7 +38420,7 @@
       </c>
       <c r="E556" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F556" s="2" t="inlineStr">
@@ -38489,7 +38489,7 @@
       </c>
       <c r="E557" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F557" s="2" t="inlineStr">
@@ -38558,7 +38558,7 @@
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F558" s="2" t="inlineStr">
@@ -38627,7 +38627,7 @@
       </c>
       <c r="E559" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F559" s="2" t="inlineStr">
@@ -38696,7 +38696,7 @@
       </c>
       <c r="E560" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F560" s="2" t="inlineStr">
@@ -38765,7 +38765,7 @@
       </c>
       <c r="E561" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F561" s="2" t="inlineStr">
@@ -38834,7 +38834,7 @@
       </c>
       <c r="E562" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F562" s="2" t="inlineStr">
@@ -38903,7 +38903,7 @@
       </c>
       <c r="E563" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F563" s="2" t="inlineStr">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="E564" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F564" s="2" t="inlineStr">
@@ -39041,7 +39041,7 @@
       </c>
       <c r="E565" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F565" s="2" t="inlineStr">
@@ -39110,7 +39110,7 @@
       </c>
       <c r="E566" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F566" s="2" t="inlineStr">
@@ -39179,7 +39179,7 @@
       </c>
       <c r="E567" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F567" s="2" t="inlineStr">
@@ -39248,7 +39248,7 @@
       </c>
       <c r="E568" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F568" s="2" t="inlineStr">
@@ -39317,7 +39317,7 @@
       </c>
       <c r="E569" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F569" s="2" t="inlineStr">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="E570" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F570" s="2" t="inlineStr">
@@ -39455,7 +39455,7 @@
       </c>
       <c r="E571" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F571" s="2" t="inlineStr">
@@ -39524,7 +39524,7 @@
       </c>
       <c r="E572" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F572" s="2" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="E573" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F573" s="2" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="E574" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F574" s="2" t="inlineStr">
@@ -39731,7 +39731,7 @@
       </c>
       <c r="E575" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F575" s="2" t="inlineStr">
@@ -39800,7 +39800,7 @@
       </c>
       <c r="E576" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F576" s="2" t="inlineStr">
@@ -39869,7 +39869,7 @@
       </c>
       <c r="E577" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F577" s="2" t="inlineStr">
@@ -39938,7 +39938,7 @@
       </c>
       <c r="E578" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F578" s="2" t="inlineStr">
@@ -40007,7 +40007,7 @@
       </c>
       <c r="E579" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F579" s="2" t="inlineStr">
@@ -40076,7 +40076,7 @@
       </c>
       <c r="E580" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F580" s="2" t="inlineStr">
@@ -40145,7 +40145,7 @@
       </c>
       <c r="E581" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F581" s="2" t="inlineStr">
@@ -40214,7 +40214,7 @@
       </c>
       <c r="E582" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F582" s="2" t="inlineStr">
@@ -40283,7 +40283,7 @@
       </c>
       <c r="E583" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F583" s="2" t="inlineStr">
@@ -40352,7 +40352,7 @@
       </c>
       <c r="E584" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F584" s="2" t="inlineStr">
@@ -40421,7 +40421,7 @@
       </c>
       <c r="E585" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F585" s="2" t="inlineStr">
@@ -40490,7 +40490,7 @@
       </c>
       <c r="E586" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F586" s="2" t="inlineStr">
@@ -40559,7 +40559,7 @@
       </c>
       <c r="E587" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F587" s="2" t="inlineStr">
@@ -40628,7 +40628,7 @@
       </c>
       <c r="E588" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F588" s="2" t="inlineStr">
@@ -40697,7 +40697,7 @@
       </c>
       <c r="E589" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F589" s="2" t="inlineStr">
@@ -40766,7 +40766,7 @@
       </c>
       <c r="E590" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F590" s="2" t="inlineStr">
@@ -40835,7 +40835,7 @@
       </c>
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F591" s="2" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F592" s="2" t="inlineStr">
@@ -40973,7 +40973,7 @@
       </c>
       <c r="E593" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F593" s="2" t="inlineStr">
@@ -41042,7 +41042,7 @@
       </c>
       <c r="E594" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F594" s="2" t="inlineStr">
@@ -41111,7 +41111,7 @@
       </c>
       <c r="E595" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F595" s="2" t="inlineStr">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="E596" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F596" s="2" t="inlineStr">
@@ -41249,7 +41249,7 @@
       </c>
       <c r="E597" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F597" s="2" t="inlineStr">
@@ -41318,7 +41318,7 @@
       </c>
       <c r="E598" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F598" s="2" t="inlineStr">
@@ -41387,7 +41387,7 @@
       </c>
       <c r="E599" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F599" s="2" t="inlineStr">
@@ -41456,7 +41456,7 @@
       </c>
       <c r="E600" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F600" s="2" t="inlineStr">
@@ -41525,7 +41525,7 @@
       </c>
       <c r="E601" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F601" s="2" t="inlineStr">
@@ -41870,7 +41870,7 @@
       </c>
       <c r="E606" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F606" s="2" t="inlineStr">
@@ -41939,7 +41939,7 @@
       </c>
       <c r="E607" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F607" s="2" t="inlineStr">
@@ -42008,7 +42008,7 @@
       </c>
       <c r="E608" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F608" s="2" t="inlineStr">
@@ -42077,7 +42077,7 @@
       </c>
       <c r="E609" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F609" s="2" t="inlineStr">
@@ -42284,7 +42284,7 @@
       </c>
       <c r="E612" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F612" s="2" t="inlineStr">
@@ -42353,7 +42353,7 @@
       </c>
       <c r="E613" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F613" s="2" t="inlineStr">
@@ -42974,7 +42974,7 @@
       </c>
       <c r="E622" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F622" s="2" t="inlineStr">
@@ -43043,7 +43043,7 @@
       </c>
       <c r="E623" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F623" s="2" t="inlineStr">
@@ -43112,7 +43112,7 @@
       </c>
       <c r="E624" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F624" s="2" t="inlineStr">
@@ -43181,7 +43181,7 @@
       </c>
       <c r="E625" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F625" s="2" t="inlineStr">
@@ -43250,7 +43250,7 @@
       </c>
       <c r="E626" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F626" s="2" t="inlineStr">
@@ -43319,7 +43319,7 @@
       </c>
       <c r="E627" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F627" s="2" t="inlineStr">
@@ -43388,7 +43388,7 @@
       </c>
       <c r="E628" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F628" s="2" t="inlineStr">
@@ -43457,7 +43457,7 @@
       </c>
       <c r="E629" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F629" s="2" t="inlineStr">
@@ -43526,7 +43526,7 @@
       </c>
       <c r="E630" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F630" s="2" t="inlineStr">
@@ -43595,7 +43595,7 @@
       </c>
       <c r="E631" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F631" s="2" t="inlineStr">
@@ -43664,7 +43664,7 @@
       </c>
       <c r="E632" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F632" s="2" t="inlineStr">
@@ -45049,7 +45049,7 @@
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G652" s="2" t="inlineStr">
@@ -45118,7 +45118,7 @@
       </c>
       <c r="F653" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G653" s="2" t="inlineStr">
@@ -45872,7 +45872,7 @@
       </c>
       <c r="E664" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F664" s="2" t="inlineStr">
@@ -45941,7 +45941,7 @@
       </c>
       <c r="E665" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F665" s="2" t="inlineStr">
@@ -46010,7 +46010,7 @@
       </c>
       <c r="E666" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F666" s="2" t="inlineStr">
@@ -46424,7 +46424,7 @@
       </c>
       <c r="E672" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F672" s="2" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="E673" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F673" s="2" t="inlineStr">
@@ -46562,7 +46562,7 @@
       </c>
       <c r="E674" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F674" s="2" t="inlineStr">
@@ -46631,7 +46631,7 @@
       </c>
       <c r="E675" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F675" s="2" t="inlineStr">
@@ -46700,7 +46700,7 @@
       </c>
       <c r="E676" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F676" s="2" t="inlineStr">
@@ -46769,7 +46769,7 @@
       </c>
       <c r="E677" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F677" s="2" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="E678" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F678" s="2" t="inlineStr">
@@ -46907,7 +46907,7 @@
       </c>
       <c r="E679" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F679" s="2" t="inlineStr">
@@ -46976,7 +46976,7 @@
       </c>
       <c r="E680" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F680" s="2" t="inlineStr">
@@ -47045,7 +47045,7 @@
       </c>
       <c r="E681" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F681" s="2" t="inlineStr">
@@ -47395,7 +47395,7 @@
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G686" s="2" t="inlineStr">
@@ -47464,7 +47464,7 @@
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G687" s="2" t="inlineStr">
@@ -47533,7 +47533,7 @@
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G688" s="2" t="inlineStr">
@@ -47602,7 +47602,7 @@
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G689" s="2" t="inlineStr">
@@ -47671,7 +47671,7 @@
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G690" s="2" t="inlineStr">
@@ -47740,7 +47740,7 @@
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G691" s="2" t="inlineStr">
@@ -47809,7 +47809,7 @@
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G692" s="2" t="inlineStr">
@@ -47878,7 +47878,7 @@
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G693" s="2" t="inlineStr">
@@ -47947,7 +47947,7 @@
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G694" s="2" t="inlineStr">
@@ -48016,7 +48016,7 @@
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G695" s="2" t="inlineStr">
@@ -48085,7 +48085,7 @@
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G696" s="2" t="inlineStr">
@@ -48154,7 +48154,7 @@
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G697" s="2" t="inlineStr">
@@ -48223,7 +48223,7 @@
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G698" s="2" t="inlineStr">
@@ -48292,7 +48292,7 @@
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G699" s="2" t="inlineStr">
@@ -48977,7 +48977,7 @@
       </c>
       <c r="E709" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F709" s="2" t="inlineStr">
@@ -49046,7 +49046,7 @@
       </c>
       <c r="E710" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F710" s="2" t="inlineStr">
@@ -49115,7 +49115,7 @@
       </c>
       <c r="E711" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F711" s="2" t="inlineStr">
@@ -51328,7 +51328,7 @@
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G743" s="2" t="inlineStr">
@@ -51397,7 +51397,7 @@
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G744" s="2" t="inlineStr">
@@ -51466,7 +51466,7 @@
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G745" s="2" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G746" s="2" t="inlineStr">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="E747" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F747" s="2" t="inlineStr">
@@ -51668,7 +51668,7 @@
       </c>
       <c r="E748" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F748" s="2" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="E749" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F749" s="2" t="inlineStr">
@@ -51806,7 +51806,7 @@
       </c>
       <c r="E750" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F750" s="2" t="inlineStr">
@@ -52432,7 +52432,7 @@
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G759" s="2" t="inlineStr">
@@ -52501,7 +52501,7 @@
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G760" s="2" t="inlineStr">
@@ -52570,7 +52570,7 @@
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G761" s="2" t="inlineStr">
@@ -52634,7 +52634,7 @@
       </c>
       <c r="E762" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F762" s="2" t="inlineStr">
@@ -52703,7 +52703,7 @@
       </c>
       <c r="E763" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F763" s="2" t="inlineStr">
@@ -52772,7 +52772,7 @@
       </c>
       <c r="E764" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F764" s="2" t="inlineStr">
@@ -52841,7 +52841,7 @@
       </c>
       <c r="E765" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F765" s="2" t="inlineStr">
@@ -52910,7 +52910,7 @@
       </c>
       <c r="E766" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F766" s="2" t="inlineStr">
@@ -54916,7 +54916,7 @@
       </c>
       <c r="F795" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G795" s="2" t="inlineStr">
@@ -54985,7 +54985,7 @@
       </c>
       <c r="F796" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G796" s="2" t="inlineStr">
@@ -55325,7 +55325,7 @@
       </c>
       <c r="E801" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F801" s="2" t="inlineStr">
@@ -55394,7 +55394,7 @@
       </c>
       <c r="E802" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F802" s="2" t="inlineStr">
@@ -55463,7 +55463,7 @@
       </c>
       <c r="E803" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F803" s="2" t="inlineStr">
@@ -55532,7 +55532,7 @@
       </c>
       <c r="E804" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F804" s="2" t="inlineStr">
@@ -55601,7 +55601,7 @@
       </c>
       <c r="E805" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F805" s="2" t="inlineStr">
@@ -55670,7 +55670,7 @@
       </c>
       <c r="E806" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F806" s="2" t="inlineStr">
@@ -57671,7 +57671,7 @@
       </c>
       <c r="E835" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F835" s="2" t="inlineStr">
@@ -57740,7 +57740,7 @@
       </c>
       <c r="E836" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F836" s="2" t="inlineStr">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="E837" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F837" s="2" t="inlineStr">
@@ -57878,7 +57878,7 @@
       </c>
       <c r="E838" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F838" s="2" t="inlineStr">
@@ -61880,7 +61880,7 @@
       </c>
       <c r="E896" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F896" s="2" t="inlineStr">
@@ -61949,7 +61949,7 @@
       </c>
       <c r="E897" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F897" s="2" t="inlineStr">
@@ -66439,7 +66439,7 @@
       </c>
       <c r="F962" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G962" s="2" t="inlineStr">
@@ -66508,7 +66508,7 @@
       </c>
       <c r="F963" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G963" s="2" t="inlineStr">
@@ -66577,7 +66577,7 @@
       </c>
       <c r="F964" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G964" s="2" t="inlineStr">
@@ -66922,7 +66922,7 @@
       </c>
       <c r="F969" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G969" s="2" t="inlineStr">
@@ -66991,7 +66991,7 @@
       </c>
       <c r="F970" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G970" s="2" t="inlineStr">
@@ -67060,7 +67060,7 @@
       </c>
       <c r="F971" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G971" s="2" t="inlineStr">
@@ -67129,7 +67129,7 @@
       </c>
       <c r="F972" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G972" s="2" t="inlineStr">
@@ -67198,7 +67198,7 @@
       </c>
       <c r="F973" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G973" s="2" t="inlineStr">
@@ -69199,7 +69199,7 @@
       </c>
       <c r="F1002" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1002" s="2" t="inlineStr">
@@ -69268,7 +69268,7 @@
       </c>
       <c r="F1003" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1003" s="2" t="inlineStr">
@@ -69337,7 +69337,7 @@
       </c>
       <c r="F1004" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1004" s="2" t="inlineStr">
@@ -69406,7 +69406,7 @@
       </c>
       <c r="F1005" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1005" s="2" t="inlineStr">
@@ -69475,7 +69475,7 @@
       </c>
       <c r="F1006" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1006" s="2" t="inlineStr">
@@ -72782,7 +72782,7 @@
       </c>
       <c r="E1054" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1054" s="2" t="inlineStr">
@@ -72851,7 +72851,7 @@
       </c>
       <c r="E1055" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1055" s="2" t="inlineStr">
@@ -72920,7 +72920,7 @@
       </c>
       <c r="E1056" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1056" s="2" t="inlineStr">
@@ -72989,7 +72989,7 @@
       </c>
       <c r="E1057" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1057" s="2" t="inlineStr">
@@ -73058,7 +73058,7 @@
       </c>
       <c r="E1058" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1058" s="2" t="inlineStr">
@@ -73127,7 +73127,7 @@
       </c>
       <c r="E1059" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1059" s="2" t="inlineStr">
@@ -73196,7 +73196,7 @@
       </c>
       <c r="E1060" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1060" s="2" t="inlineStr">
@@ -73265,7 +73265,7 @@
       </c>
       <c r="E1061" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1061" s="2" t="inlineStr">
@@ -74167,7 +74167,7 @@
       </c>
       <c r="F1074" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1074" s="2" t="inlineStr">
@@ -74236,7 +74236,7 @@
       </c>
       <c r="F1075" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1075" s="2" t="inlineStr">
@@ -74305,7 +74305,7 @@
       </c>
       <c r="F1076" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1076" s="2" t="inlineStr">
@@ -74374,7 +74374,7 @@
       </c>
       <c r="F1077" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1077" s="2" t="inlineStr">
@@ -74443,7 +74443,7 @@
       </c>
       <c r="F1078" s="2" t="inlineStr">
         <is>
-          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1078" s="2" t="inlineStr">
@@ -74507,7 +74507,7 @@
       </c>
       <c r="E1079" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1079" s="2" t="inlineStr">
@@ -74576,7 +74576,7 @@
       </c>
       <c r="E1080" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1080" s="2" t="inlineStr">
@@ -74645,7 +74645,7 @@
       </c>
       <c r="E1081" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1081" s="2" t="inlineStr">
@@ -74714,7 +74714,7 @@
       </c>
       <c r="E1082" s="2" t="inlineStr">
         <is>
-          <t>THIAGO-REGIONAL CENTRO OESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1082" s="2" t="inlineStr">
@@ -74788,7 +74788,7 @@
       </c>
       <c r="F1083" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G1083" s="2" t="inlineStr">
@@ -74857,7 +74857,7 @@
       </c>
       <c r="F1084" s="2" t="inlineStr">
         <is>
-          <t>370- MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="G1084" s="2" t="inlineStr">
@@ -81274,7 +81274,7 @@
       </c>
       <c r="F1177" s="2" t="inlineStr">
         <is>
-          <t>345- LEVET REPRESENTACOES E COMERCIO LTDA</t>
+          <t>345 LEVET REPRESENTACOES E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="G1177" s="2" t="inlineStr">

--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q1179"/>
+  <dimension ref="A1:Q1216"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -347,7 +347,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -416,7 +416,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
@@ -81452,6 +81452,2559 @@
         <v>1.0</v>
       </c>
       <c r="Q1179" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1180" s="2" t="n">
+        <v>564170.0</v>
+      </c>
+      <c r="C1180" s="2" t="inlineStr">
+        <is>
+          <t>44860000411</t>
+        </is>
+      </c>
+      <c r="D1180" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1180" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1180" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1180" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1180" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1180" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1180" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1180" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1180" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1180" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1180" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1180" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1180" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1180" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1181" s="2" t="n">
+        <v>564170.0</v>
+      </c>
+      <c r="C1181" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1181" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1181" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1181" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1181" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1181" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1181" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1181" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1181" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1181" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1181" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1181" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1181" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1181" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1181" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1182" s="2" t="n">
+        <v>564170.0</v>
+      </c>
+      <c r="C1182" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1182" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1182" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1182" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1182" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1182" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1182" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1182" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1182" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1182" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1182" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1182" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1182" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1182" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1182" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1183" s="2" t="n">
+        <v>564170.0</v>
+      </c>
+      <c r="C1183" s="2" t="inlineStr">
+        <is>
+          <t>44860013330</t>
+        </is>
+      </c>
+      <c r="D1183" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC MARFIM/OURO</t>
+        </is>
+      </c>
+      <c r="E1183" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1183" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1183" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1183" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1183" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1183" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1183" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1183" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1183" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1183" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1183" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1183" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1183" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1184" s="2" t="n">
+        <v>564219.0</v>
+      </c>
+      <c r="C1184" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1184" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1184" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1184" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1184" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1184" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1184" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1184" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1184" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1184" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1184" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1184" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1184" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1184" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1184" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1185" s="2" t="n">
+        <v>564219.0</v>
+      </c>
+      <c r="C1185" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1185" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1185" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1185" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1185" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1185" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1185" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1185" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1185" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1185" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1185" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1185" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1185" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1185" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1185" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1186" s="2" t="n">
+        <v>564220.0</v>
+      </c>
+      <c r="C1186" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1186" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1186" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1186" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1186" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1186" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1186" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1186" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K1186" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="L1186" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="M1186" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="N1186" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O1186" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="P1186" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="Q1186" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1187" s="2" t="n">
+        <v>564220.0</v>
+      </c>
+      <c r="C1187" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1187" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1187" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1187" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1187" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1187" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1187" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1187" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1187" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1187" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="M1187" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="N1187" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O1187" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="P1187" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q1187" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1188" s="2" t="n">
+        <v>564221.0</v>
+      </c>
+      <c r="C1188" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1188" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1188" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1188" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1188" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1188" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1188" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1188" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1188" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1188" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="M1188" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="N1188" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="O1188" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="P1188" s="2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="Q1188" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1189" s="2" t="n">
+        <v>564230.0</v>
+      </c>
+      <c r="C1189" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1189" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1189" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1189" s="2" t="inlineStr">
+        <is>
+          <t>19 HAMILTON BIRIGUI REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1189" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1189" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1189" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1189" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1189" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1189" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1189" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1189" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1189" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1189" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1189" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1190" s="2" t="n">
+        <v>564230.0</v>
+      </c>
+      <c r="C1190" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1190" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1190" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1190" s="2" t="inlineStr">
+        <is>
+          <t>19 HAMILTON BIRIGUI REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1190" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1190" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1190" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1190" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1190" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1190" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1190" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1190" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1190" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1190" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1190" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1191" s="2" t="n">
+        <v>564231.0</v>
+      </c>
+      <c r="C1191" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1191" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1191" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1191" s="2" t="inlineStr">
+        <is>
+          <t>19 HAMILTON BIRIGUI REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1191" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1191" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1191" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1191" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1191" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1191" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1191" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1191" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1191" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1191" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1191" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1192" s="2" t="n">
+        <v>564267.0</v>
+      </c>
+      <c r="C1192" s="2" t="inlineStr">
+        <is>
+          <t>08760010007</t>
+        </is>
+      </c>
+      <c r="D1192" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1192" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1192" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1192" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1192" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1192" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1192" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1192" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1192" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1192" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1192" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1192" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1192" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1192" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1193" s="2" t="n">
+        <v>564267.0</v>
+      </c>
+      <c r="C1193" s="2" t="inlineStr">
+        <is>
+          <t>08760014005</t>
+        </is>
+      </c>
+      <c r="D1193" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE NUDE</t>
+        </is>
+      </c>
+      <c r="E1193" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1193" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1193" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1193" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1193" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1193" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1193" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1193" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1193" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1193" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1193" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1193" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1193" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1194" s="2" t="n">
+        <v>564267.0</v>
+      </c>
+      <c r="C1194" s="2" t="inlineStr">
+        <is>
+          <t>08760020008</t>
+        </is>
+      </c>
+      <c r="D1194" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE ROSA</t>
+        </is>
+      </c>
+      <c r="E1194" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1194" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1194" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1194" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1194" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1194" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1194" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1194" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1194" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1194" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1194" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1194" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1194" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1195" s="2" t="n">
+        <v>564268.0</v>
+      </c>
+      <c r="C1195" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1195" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1195" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1195" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1195" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1195" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1195" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1195" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1195" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1195" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1195" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1195" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1195" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1195" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1195" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1196" s="2" t="n">
+        <v>564268.0</v>
+      </c>
+      <c r="C1196" s="2" t="inlineStr">
+        <is>
+          <t>43860000017</t>
+        </is>
+      </c>
+      <c r="D1196" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1196" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1196" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1196" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1196" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1196" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1196" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1196" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1196" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1196" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1196" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1196" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1196" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1196" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1197" s="2" t="n">
+        <v>564268.0</v>
+      </c>
+      <c r="C1197" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1197" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1197" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1197" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1197" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1197" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1197" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1197" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1197" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1197" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1197" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1197" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1197" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1197" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1197" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1198" s="2" t="n">
+        <v>564269.0</v>
+      </c>
+      <c r="C1198" s="2" t="inlineStr">
+        <is>
+          <t>45560000017</t>
+        </is>
+      </c>
+      <c r="D1198" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1198" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1198" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1198" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1198" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1198" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1198" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1198" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1198" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1198" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1198" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1198" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1198" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1198" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1199" s="2" t="n">
+        <v>564270.0</v>
+      </c>
+      <c r="C1199" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1199" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1199" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1199" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1199" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1199" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1199" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1199" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1199" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1199" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1199" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1199" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1199" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1199" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1199" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1200" s="2" t="n">
+        <v>564270.0</v>
+      </c>
+      <c r="C1200" s="2" t="inlineStr">
+        <is>
+          <t>44860000341</t>
+        </is>
+      </c>
+      <c r="D1200" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1200" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1200" s="2" t="inlineStr">
+        <is>
+          <t>15 J. JIREH REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1200" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1200" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1200" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1200" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1200" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1200" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1200" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1200" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1200" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1200" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1200" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1201" s="2" t="n">
+        <v>564310.0</v>
+      </c>
+      <c r="C1201" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1201" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1201" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1201" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1201" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1201" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1201" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1201" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1201" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1201" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1201" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1201" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1201" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1201" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1201" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1202" s="2" t="n">
+        <v>564310.0</v>
+      </c>
+      <c r="C1202" s="2" t="inlineStr">
+        <is>
+          <t>08760004005</t>
+        </is>
+      </c>
+      <c r="D1202" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE NUDE</t>
+        </is>
+      </c>
+      <c r="E1202" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1202" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1202" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1202" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1202" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1202" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1202" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1202" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1202" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1202" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1202" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1202" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1202" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1203" s="2" t="n">
+        <v>564310.0</v>
+      </c>
+      <c r="C1203" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1203" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1203" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1203" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1203" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1203" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1203" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1203" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1203" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1203" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1203" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1203" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1203" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1203" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1203" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1204" s="2" t="n">
+        <v>564311.0</v>
+      </c>
+      <c r="C1204" s="2" t="inlineStr">
+        <is>
+          <t>43860000008</t>
+        </is>
+      </c>
+      <c r="D1204" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC ROSA</t>
+        </is>
+      </c>
+      <c r="E1204" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1204" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1204" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1204" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1204" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1204" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1204" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1204" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1204" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1204" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1204" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1204" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1204" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="2" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="B1205" s="2" t="n">
+        <v>564311.0</v>
+      </c>
+      <c r="C1205" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1205" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1205" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1205" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1205" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1205" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1205" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1205" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1205" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1205" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1205" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1205" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1205" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1205" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1205" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="2" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="B1206" s="2" t="n">
+        <v>564436.0</v>
+      </c>
+      <c r="C1206" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1206" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1206" s="2" t="inlineStr">
+        <is>
+          <t>MS/MT</t>
+        </is>
+      </c>
+      <c r="F1206" s="2" t="inlineStr">
+        <is>
+          <t>266 LORAN DA SILVA SANTOS REPRESENTAÇÕES EIRELI</t>
+        </is>
+      </c>
+      <c r="G1206" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1206" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1206" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1206" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1206" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1206" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1206" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1206" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1206" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1206" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1206" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1207" s="2" t="n">
+        <v>564521.0</v>
+      </c>
+      <c r="C1207" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1207" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1207" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1207" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1207" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1207" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1207" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1207" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1207" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1207" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1207" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1207" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1207" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1207" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1207" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1208" s="2" t="n">
+        <v>564521.0</v>
+      </c>
+      <c r="C1208" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1208" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1208" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1208" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1208" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1208" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1208" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1208" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1208" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1208" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1208" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1208" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1208" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1208" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1208" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1209" s="2" t="n">
+        <v>564522.0</v>
+      </c>
+      <c r="C1209" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1209" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1209" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1209" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1209" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1209" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1209" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1209" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1209" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1209" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1209" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1209" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1209" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1209" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1209" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1210" s="2" t="n">
+        <v>564522.0</v>
+      </c>
+      <c r="C1210" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1210" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1210" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1210" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1210" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1210" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1210" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1210" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1210" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1210" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1210" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1210" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1210" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1210" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1210" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1211" s="2" t="n">
+        <v>564536.0</v>
+      </c>
+      <c r="C1211" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1211" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1211" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1211" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1211" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1211" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1211" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1211" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1211" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1211" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1211" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1211" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1211" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1211" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1211" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1212" s="2" t="n">
+        <v>564536.0</v>
+      </c>
+      <c r="C1212" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1212" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1212" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1212" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1212" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1212" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1212" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1212" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1212" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1212" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1212" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1212" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1212" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1212" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1212" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1213" s="2" t="n">
+        <v>564537.0</v>
+      </c>
+      <c r="C1213" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1213" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1213" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1213" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1213" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1213" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1213" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1213" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1213" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1213" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1213" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1213" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1213" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1213" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1213" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1214" s="2" t="n">
+        <v>564537.0</v>
+      </c>
+      <c r="C1214" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1214" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1214" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1214" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1214" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1214" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1214" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1214" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1214" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1214" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1214" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1214" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1214" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1214" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1214" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1215" s="2" t="n">
+        <v>564538.0</v>
+      </c>
+      <c r="C1215" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1215" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1215" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1215" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1215" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1215" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1215" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1215" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1215" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1215" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1215" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1215" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1215" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1215" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1215" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="2" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
+      <c r="B1216" s="2" t="n">
+        <v>564538.0</v>
+      </c>
+      <c r="C1216" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1216" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1216" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1216" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1216" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1216" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1216" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1216" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1216" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1216" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1216" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1216" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1216" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1216" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1216" s="2" t="n">
         <v>12.0</v>
       </c>
     </row>

--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q1216"/>
+  <dimension ref="A1:Q1265"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
@@ -13457,7 +13457,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
@@ -18011,7 +18011,7 @@
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr">
@@ -22289,7 +22289,7 @@
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr">
@@ -84005,6 +84005,3387 @@
         <v>2.0</v>
       </c>
       <c r="Q1216" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1217" s="2" t="n">
+        <v>564656.0</v>
+      </c>
+      <c r="C1217" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1217" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1217" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1217" s="2" t="inlineStr">
+        <is>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1217" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1217" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1217" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1217" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1217" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1217" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1217" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1217" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1217" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1217" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1217" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1218" s="2" t="n">
+        <v>564656.0</v>
+      </c>
+      <c r="C1218" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1218" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1218" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1218" s="2" t="inlineStr">
+        <is>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1218" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1218" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1218" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1218" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1218" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1218" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1218" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1218" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1218" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1218" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1218" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1219" s="2" t="n">
+        <v>564657.0</v>
+      </c>
+      <c r="C1219" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1219" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1219" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1219" s="2" t="inlineStr">
+        <is>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1219" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1219" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1219" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1219" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1219" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1219" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1219" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1219" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1219" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1219" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1219" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1220" s="2" t="n">
+        <v>564657.0</v>
+      </c>
+      <c r="C1220" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1220" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1220" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1220" s="2" t="inlineStr">
+        <is>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1220" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1220" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1220" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1220" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1220" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1220" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1220" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1220" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1220" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1220" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1220" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1221" s="2" t="n">
+        <v>564658.0</v>
+      </c>
+      <c r="C1221" s="2" t="inlineStr">
+        <is>
+          <t>45560000007</t>
+        </is>
+      </c>
+      <c r="D1221" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO PRETO</t>
+        </is>
+      </c>
+      <c r="E1221" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1221" s="2" t="inlineStr">
+        <is>
+          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+        </is>
+      </c>
+      <c r="G1221" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1221" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1221" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1221" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1221" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1221" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1221" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1221" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1221" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1221" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1221" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1222" s="2" t="n">
+        <v>564700.0</v>
+      </c>
+      <c r="C1222" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D1222" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1222" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F1222" s="2" t="inlineStr">
+        <is>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G1222" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1222" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1222" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1222" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1222" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1222" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1222" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1222" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1222" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1222" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1222" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1223" s="2" t="n">
+        <v>564701.0</v>
+      </c>
+      <c r="C1223" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1223" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1223" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F1223" s="2" t="inlineStr">
+        <is>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G1223" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1223" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1223" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1223" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1223" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1223" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1223" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1223" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1223" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1223" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1223" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1224" s="2" t="n">
+        <v>564712.0</v>
+      </c>
+      <c r="C1224" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D1224" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1224" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F1224" s="2" t="inlineStr">
+        <is>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G1224" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1224" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1224" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1224" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1224" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1224" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1224" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1224" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1224" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1224" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1224" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1225" s="2" t="n">
+        <v>564713.0</v>
+      </c>
+      <c r="C1225" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1225" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1225" s="2" t="inlineStr">
+        <is>
+          <t>SUL</t>
+        </is>
+      </c>
+      <c r="F1225" s="2" t="inlineStr">
+        <is>
+          <t>370 MESSIAS BECKER COMERCIO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G1225" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1225" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1225" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1225" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1225" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1225" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1225" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1225" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1225" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1225" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1225" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1226" s="2" t="n">
+        <v>564822.0</v>
+      </c>
+      <c r="C1226" s="2" t="inlineStr">
+        <is>
+          <t>44860000341</t>
+        </is>
+      </c>
+      <c r="D1226" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1226" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1226" s="2" t="inlineStr">
+        <is>
+          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1226" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1226" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1226" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1226" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1226" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1226" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1226" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1226" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1226" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1226" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1226" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1227" s="2" t="n">
+        <v>564822.0</v>
+      </c>
+      <c r="C1227" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1227" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1227" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1227" s="2" t="inlineStr">
+        <is>
+          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1227" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1227" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1227" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1227" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1227" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1227" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1227" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1227" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1227" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1227" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1227" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1228" s="2" t="n">
+        <v>564845.0</v>
+      </c>
+      <c r="C1228" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1228" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1228" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1228" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1228" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1228" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1228" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1228" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1228" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1228" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1228" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1228" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1228" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1228" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1228" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1229" s="2" t="n">
+        <v>564845.0</v>
+      </c>
+      <c r="C1229" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1229" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1229" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1229" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1229" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1229" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1229" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1229" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1229" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1229" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1229" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1229" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1229" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1229" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1229" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1230" s="2" t="n">
+        <v>564846.0</v>
+      </c>
+      <c r="C1230" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1230" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1230" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1230" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1230" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1230" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1230" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1230" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1230" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1230" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1230" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1230" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1230" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1230" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1230" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1231" s="2" t="n">
+        <v>564847.0</v>
+      </c>
+      <c r="C1231" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1231" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1231" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1231" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1231" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1231" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1231" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1231" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1231" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1231" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1231" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1231" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1231" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1231" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1231" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1232" s="2" t="n">
+        <v>564847.0</v>
+      </c>
+      <c r="C1232" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1232" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1232" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1232" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1232" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1232" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1232" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1232" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1232" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1232" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1232" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1232" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1232" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1232" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1232" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1233" s="2" t="n">
+        <v>564848.0</v>
+      </c>
+      <c r="C1233" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1233" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1233" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1233" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1233" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1233" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1233" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1233" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1233" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1233" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1233" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1233" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1233" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1233" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1233" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1234" s="2" t="n">
+        <v>564848.0</v>
+      </c>
+      <c r="C1234" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1234" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1234" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1234" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1234" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1234" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1234" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1234" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1234" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1234" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1234" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1234" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1234" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1234" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1234" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1235" s="2" t="n">
+        <v>564849.0</v>
+      </c>
+      <c r="C1235" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1235" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1235" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1235" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1235" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1235" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1235" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1235" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1235" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1235" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1235" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1235" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1235" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1235" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1235" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1236" s="2" t="n">
+        <v>564849.0</v>
+      </c>
+      <c r="C1236" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1236" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1236" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1236" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1236" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1236" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1236" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1236" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1236" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1236" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1236" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1236" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1236" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1236" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1236" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1237" s="2" t="n">
+        <v>564850.0</v>
+      </c>
+      <c r="C1237" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1237" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1237" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1237" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1237" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1237" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1237" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1237" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1237" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1237" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1237" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1237" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1237" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1237" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1237" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1238" s="2" t="n">
+        <v>564850.0</v>
+      </c>
+      <c r="C1238" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1238" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1238" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1238" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1238" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1238" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1238" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1238" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1238" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1238" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1238" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1238" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1238" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1238" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1238" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1239" s="2" t="n">
+        <v>564851.0</v>
+      </c>
+      <c r="C1239" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1239" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1239" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1239" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1239" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1239" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1239" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1239" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1239" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1239" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1239" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1239" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1239" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1239" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1239" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1240" s="2" t="n">
+        <v>564852.0</v>
+      </c>
+      <c r="C1240" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1240" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1240" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1240" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1240" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1240" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1240" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1240" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1240" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1240" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1240" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1240" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1240" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1240" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1240" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1241" s="2" t="n">
+        <v>564852.0</v>
+      </c>
+      <c r="C1241" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1241" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1241" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1241" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1241" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1241" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1241" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1241" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1241" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1241" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1241" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1241" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1241" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1241" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1241" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1242" s="2" t="n">
+        <v>564853.0</v>
+      </c>
+      <c r="C1242" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1242" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1242" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1242" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1242" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1242" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1242" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1242" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1242" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1242" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1242" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1242" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1242" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1242" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1242" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1243" s="2" t="n">
+        <v>564854.0</v>
+      </c>
+      <c r="C1243" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1243" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1243" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1243" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1243" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1243" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1243" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1243" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1243" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1243" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1243" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1243" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1243" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1243" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1243" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1244" s="2" t="n">
+        <v>564854.0</v>
+      </c>
+      <c r="C1244" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1244" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1244" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1244" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1244" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1244" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1244" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1244" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1244" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1244" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1244" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1244" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1244" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1244" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1244" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1245" s="2" t="n">
+        <v>564855.0</v>
+      </c>
+      <c r="C1245" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1245" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1245" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1245" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1245" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1245" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1245" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1245" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1245" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1245" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1245" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1245" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1245" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1245" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1245" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1246" s="2" t="n">
+        <v>564855.0</v>
+      </c>
+      <c r="C1246" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1246" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1246" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1246" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1246" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1246" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1246" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1246" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1246" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1246" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1246" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1246" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1246" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1246" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1246" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1247" s="2" t="n">
+        <v>564856.0</v>
+      </c>
+      <c r="C1247" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1247" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1247" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1247" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1247" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1247" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1247" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1247" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1247" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1247" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1247" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1247" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1247" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1247" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1247" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1248" s="2" t="n">
+        <v>564856.0</v>
+      </c>
+      <c r="C1248" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1248" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1248" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1248" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1248" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1248" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1248" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1248" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1248" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1248" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1248" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1248" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1248" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1248" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1248" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1249" s="2" t="n">
+        <v>564857.0</v>
+      </c>
+      <c r="C1249" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1249" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1249" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1249" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1249" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1249" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1249" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1249" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1249" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1249" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1249" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1249" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1249" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1249" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1249" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1250" s="2" t="n">
+        <v>564857.0</v>
+      </c>
+      <c r="C1250" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1250" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1250" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1250" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1250" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1250" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1250" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1250" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1250" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1250" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1250" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1250" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1250" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1250" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1250" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1251" s="2" t="n">
+        <v>564858.0</v>
+      </c>
+      <c r="C1251" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1251" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1251" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1251" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1251" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1251" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1251" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1251" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1251" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1251" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1251" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1251" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1251" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1251" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1251" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1252" s="2" t="n">
+        <v>564858.0</v>
+      </c>
+      <c r="C1252" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1252" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1252" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1252" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1252" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1252" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1252" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1252" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1252" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1252" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1252" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1252" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1252" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1252" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1252" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1253" s="2" t="n">
+        <v>564859.0</v>
+      </c>
+      <c r="C1253" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1253" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1253" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1253" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1253" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1253" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1253" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1253" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1253" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1253" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1253" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1253" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1253" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1253" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1253" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1254" s="2" t="n">
+        <v>564859.0</v>
+      </c>
+      <c r="C1254" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1254" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1254" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1254" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1254" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1254" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1254" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1254" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1254" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1254" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1254" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1254" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1254" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1254" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1254" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1255" s="2" t="n">
+        <v>564860.0</v>
+      </c>
+      <c r="C1255" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1255" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1255" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1255" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1255" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1255" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1255" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1255" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1255" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1255" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1255" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1255" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1255" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1255" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1255" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1256" s="2" t="n">
+        <v>564860.0</v>
+      </c>
+      <c r="C1256" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1256" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1256" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1256" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1256" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1256" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1256" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1256" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1256" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1256" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1256" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1256" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1256" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1256" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1256" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1257" s="2" t="n">
+        <v>564861.0</v>
+      </c>
+      <c r="C1257" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1257" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1257" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1257" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1257" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1257" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1257" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1257" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1257" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1257" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1257" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1257" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1257" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1257" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1257" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1258" s="2" t="n">
+        <v>564861.0</v>
+      </c>
+      <c r="C1258" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1258" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1258" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1258" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1258" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1258" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1258" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1258" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1258" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1258" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1258" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1258" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1258" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1258" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1258" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1259" s="2" t="n">
+        <v>564862.0</v>
+      </c>
+      <c r="C1259" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1259" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1259" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1259" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1259" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1259" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1259" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1259" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1259" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1259" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1259" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1259" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1259" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1259" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1259" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1260" s="2" t="n">
+        <v>564862.0</v>
+      </c>
+      <c r="C1260" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1260" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1260" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1260" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1260" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1260" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1260" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1260" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1260" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1260" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1260" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1260" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1260" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1260" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1260" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1261" s="2" t="n">
+        <v>564947.0</v>
+      </c>
+      <c r="C1261" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1261" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1261" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1261" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1261" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1261" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1261" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1261" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1261" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1261" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M1261" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="N1261" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1261" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P1261" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1261" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1262" s="2" t="n">
+        <v>564947.0</v>
+      </c>
+      <c r="C1262" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1262" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1262" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1262" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1262" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1262" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1262" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1262" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1262" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1262" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1262" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1262" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1262" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1262" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1262" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1263" s="2" t="n">
+        <v>564948.0</v>
+      </c>
+      <c r="C1263" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1263" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1263" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1263" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1263" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1263" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1263" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1263" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1263" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1263" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1263" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1263" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1263" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1263" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1263" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1264" s="2" t="n">
+        <v>564984.0</v>
+      </c>
+      <c r="C1264" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1264" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1264" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1264" s="2" t="inlineStr">
+        <is>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+        </is>
+      </c>
+      <c r="G1264" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1264" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1264" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1264" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1264" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1264" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1264" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1264" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1264" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1264" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1264" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B1265" s="2" t="n">
+        <v>564984.0</v>
+      </c>
+      <c r="C1265" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1265" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1265" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1265" s="2" t="inlineStr">
+        <is>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+        </is>
+      </c>
+      <c r="G1265" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1265" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1265" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1265" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1265" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1265" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1265" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1265" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1265" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1265" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1265" s="2" t="n">
         <v>12.0</v>
       </c>
     </row>

--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q1265"/>
+  <dimension ref="A1:Q1293"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
@@ -15527,7 +15527,7 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
@@ -17459,7 +17459,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
@@ -87386,6 +87386,1938 @@
         <v>2.0</v>
       </c>
       <c r="Q1265" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1266" s="2" t="n">
+        <v>565160.0</v>
+      </c>
+      <c r="C1266" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1266" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1266" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1266" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1266" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1266" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1266" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1266" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1266" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1266" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1266" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1266" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1266" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1266" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1266" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1267" s="2" t="n">
+        <v>565161.0</v>
+      </c>
+      <c r="C1267" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1267" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1267" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1267" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1267" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1267" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1267" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1267" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1267" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1267" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1267" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1267" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1267" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1267" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1267" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1268" s="2" t="n">
+        <v>565161.0</v>
+      </c>
+      <c r="C1268" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1268" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1268" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1268" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1268" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1268" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1268" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1268" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1268" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1268" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1268" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1268" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1268" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1268" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1268" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1269" s="2" t="n">
+        <v>565185.0</v>
+      </c>
+      <c r="C1269" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1269" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1269" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1269" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1269" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1269" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1269" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1269" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1269" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1269" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1269" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1269" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1269" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1269" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1269" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1270" s="2" t="n">
+        <v>565185.0</v>
+      </c>
+      <c r="C1270" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1270" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1270" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1270" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1270" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1270" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1270" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1270" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1270" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1270" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1270" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1270" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1270" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1270" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1270" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1271" s="2" t="n">
+        <v>565194.0</v>
+      </c>
+      <c r="C1271" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1271" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1271" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1271" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1271" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1271" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1271" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1271" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1271" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1271" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1271" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1271" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1271" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1271" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1271" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1272" s="2" t="n">
+        <v>565194.0</v>
+      </c>
+      <c r="C1272" s="2" t="inlineStr">
+        <is>
+          <t>08760020007</t>
+        </is>
+      </c>
+      <c r="D1272" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1272" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1272" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1272" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1272" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1272" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1272" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1272" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1272" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1272" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1272" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1272" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1272" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1272" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1273" s="2" t="n">
+        <v>565214.0</v>
+      </c>
+      <c r="C1273" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1273" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1273" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1273" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1273" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1273" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1273" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1273" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1273" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1273" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1273" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1273" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1273" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1273" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1273" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1274" s="2" t="n">
+        <v>565215.0</v>
+      </c>
+      <c r="C1274" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1274" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1274" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1274" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1274" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1274" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1274" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1274" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1274" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1274" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1274" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1274" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1274" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1274" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1274" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1275" s="2" t="n">
+        <v>565216.0</v>
+      </c>
+      <c r="C1275" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1275" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1275" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1275" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1275" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1275" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1275" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1275" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1275" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1275" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1275" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1275" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1275" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1275" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1275" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1276" s="2" t="n">
+        <v>565217.0</v>
+      </c>
+      <c r="C1276" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1276" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1276" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1276" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1276" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1276" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1276" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1276" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1276" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1276" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1276" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1276" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1276" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1276" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1276" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1277" s="2" t="n">
+        <v>565217.0</v>
+      </c>
+      <c r="C1277" s="2" t="inlineStr">
+        <is>
+          <t>44860013330</t>
+        </is>
+      </c>
+      <c r="D1277" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC MARFIM/OURO</t>
+        </is>
+      </c>
+      <c r="E1277" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1277" s="2" t="inlineStr">
+        <is>
+          <t>240 RAMON MAIA DE LIMA</t>
+        </is>
+      </c>
+      <c r="G1277" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1277" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1277" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1277" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1277" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1277" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1277" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1277" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1277" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1277" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1277" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1278" s="2" t="n">
+        <v>565242.0</v>
+      </c>
+      <c r="C1278" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1278" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1278" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1278" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1278" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1278" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1278" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1278" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1278" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1278" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1278" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1278" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1278" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1278" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1278" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1279" s="2" t="n">
+        <v>565242.0</v>
+      </c>
+      <c r="C1279" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1279" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1279" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1279" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1279" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1279" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1279" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1279" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1279" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1279" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1279" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1279" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1279" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1279" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1279" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1280" s="2" t="n">
+        <v>565242.0</v>
+      </c>
+      <c r="C1280" s="2" t="inlineStr">
+        <is>
+          <t>44860014005</t>
+        </is>
+      </c>
+      <c r="D1280" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1280" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1280" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1280" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1280" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1280" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1280" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1280" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1280" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1280" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1280" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1280" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1280" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1280" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1281" s="2" t="n">
+        <v>565243.0</v>
+      </c>
+      <c r="C1281" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1281" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1281" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1281" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1281" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1281" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1281" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1281" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1281" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1281" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1281" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1281" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1281" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1281" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1281" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1282" s="2" t="n">
+        <v>565309.0</v>
+      </c>
+      <c r="C1282" s="2" t="inlineStr">
+        <is>
+          <t>44860000341</t>
+        </is>
+      </c>
+      <c r="D1282" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1282" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1282" s="2" t="inlineStr">
+        <is>
+          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1282" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1282" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1282" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1282" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1282" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1282" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1282" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1282" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1282" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1282" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1282" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1283" s="2" t="n">
+        <v>565309.0</v>
+      </c>
+      <c r="C1283" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1283" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1283" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1283" s="2" t="inlineStr">
+        <is>
+          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+        </is>
+      </c>
+      <c r="G1283" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1283" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1283" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1283" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1283" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1283" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1283" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1283" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1283" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1283" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1283" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1284" s="2" t="n">
+        <v>565331.0</v>
+      </c>
+      <c r="C1284" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1284" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1284" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1284" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1284" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1284" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1284" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1284" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1284" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1284" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1284" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1284" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1284" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1284" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1284" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1285" s="2" t="n">
+        <v>565331.0</v>
+      </c>
+      <c r="C1285" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1285" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1285" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1285" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1285" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1285" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1285" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1285" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1285" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1285" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1285" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1285" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1285" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1285" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1285" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1286" s="2" t="n">
+        <v>565332.0</v>
+      </c>
+      <c r="C1286" s="2" t="inlineStr">
+        <is>
+          <t>43860010411</t>
+        </is>
+      </c>
+      <c r="D1286" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1286" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1286" s="2" t="inlineStr">
+        <is>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+        </is>
+      </c>
+      <c r="G1286" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1286" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1286" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1286" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1286" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1286" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1286" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1286" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1286" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1286" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1286" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1287" s="2" t="n">
+        <v>565345.0</v>
+      </c>
+      <c r="C1287" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1287" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1287" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1287" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1287" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1287" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1287" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1287" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1287" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1287" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1287" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1287" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1287" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1287" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1287" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1288" s="2" t="n">
+        <v>565346.0</v>
+      </c>
+      <c r="C1288" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1288" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1288" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1288" s="2" t="inlineStr">
+        <is>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1288" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1288" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1288" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1288" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1288" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1288" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1288" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1288" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1288" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1288" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1288" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1289" s="2" t="n">
+        <v>565352.0</v>
+      </c>
+      <c r="C1289" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1289" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1289" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1289" s="2" t="inlineStr">
+        <is>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+        </is>
+      </c>
+      <c r="G1289" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1289" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1289" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1289" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1289" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1289" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1289" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1289" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1289" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1289" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1289" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1290" s="2" t="n">
+        <v>565352.0</v>
+      </c>
+      <c r="C1290" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1290" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1290" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1290" s="2" t="inlineStr">
+        <is>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+        </is>
+      </c>
+      <c r="G1290" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1290" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1290" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1290" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1290" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1290" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1290" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1290" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1290" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1290" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1290" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1291" s="2" t="n">
+        <v>565353.0</v>
+      </c>
+      <c r="C1291" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1291" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1291" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1291" s="2" t="inlineStr">
+        <is>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+        </is>
+      </c>
+      <c r="G1291" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1291" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1291" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1291" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1291" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1291" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1291" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1291" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1291" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1291" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1291" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1292" s="2" t="n">
+        <v>565389.0</v>
+      </c>
+      <c r="C1292" s="2" t="inlineStr">
+        <is>
+          <t>44860003330</t>
+        </is>
+      </c>
+      <c r="D1292" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC MARFIM/OURO</t>
+        </is>
+      </c>
+      <c r="E1292" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1292" s="2" t="inlineStr">
+        <is>
+          <t>197 FABRICIO RIZZATO RODRIGUES</t>
+        </is>
+      </c>
+      <c r="G1292" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1292" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1292" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1292" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1292" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1292" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1292" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1292" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1292" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1292" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1292" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="B1293" s="2" t="n">
+        <v>565390.0</v>
+      </c>
+      <c r="C1293" s="2" t="inlineStr">
+        <is>
+          <t>45560000017</t>
+        </is>
+      </c>
+      <c r="D1293" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1293" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1293" s="2" t="inlineStr">
+        <is>
+          <t>197 FABRICIO RIZZATO RODRIGUES</t>
+        </is>
+      </c>
+      <c r="G1293" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1293" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1293" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1293" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1293" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1293" s="2" t="n">
         <v>12.0</v>
       </c>
     </row>

--- a/Dados_Rebecca.xlsx
+++ b/Dados_Rebecca.xlsx
@@ -83,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q1293"/>
+  <dimension ref="A1:Q1346"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
@@ -14975,7 +14975,7 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>ABERTO</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
@@ -47395,7 +47395,7 @@
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G686" s="2" t="inlineStr">
@@ -47464,7 +47464,7 @@
       </c>
       <c r="F687" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G687" s="2" t="inlineStr">
@@ -47533,7 +47533,7 @@
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G688" s="2" t="inlineStr">
@@ -47602,7 +47602,7 @@
       </c>
       <c r="F689" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G689" s="2" t="inlineStr">
@@ -47671,7 +47671,7 @@
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G690" s="2" t="inlineStr">
@@ -47740,7 +47740,7 @@
       </c>
       <c r="F691" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G691" s="2" t="inlineStr">
@@ -47809,7 +47809,7 @@
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G692" s="2" t="inlineStr">
@@ -47878,7 +47878,7 @@
       </c>
       <c r="F693" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G693" s="2" t="inlineStr">
@@ -47947,7 +47947,7 @@
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G694" s="2" t="inlineStr">
@@ -48016,7 +48016,7 @@
       </c>
       <c r="F695" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G695" s="2" t="inlineStr">
@@ -48085,7 +48085,7 @@
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G696" s="2" t="inlineStr">
@@ -48154,7 +48154,7 @@
       </c>
       <c r="F697" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G697" s="2" t="inlineStr">
@@ -48223,7 +48223,7 @@
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G698" s="2" t="inlineStr">
@@ -48292,7 +48292,7 @@
       </c>
       <c r="F699" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G699" s="2" t="inlineStr">
@@ -51328,7 +51328,7 @@
       </c>
       <c r="F743" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G743" s="2" t="inlineStr">
@@ -51397,7 +51397,7 @@
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G744" s="2" t="inlineStr">
@@ -51466,7 +51466,7 @@
       </c>
       <c r="F745" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G745" s="2" t="inlineStr">
@@ -51535,7 +51535,7 @@
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G746" s="2" t="inlineStr">
@@ -52432,7 +52432,7 @@
       </c>
       <c r="F759" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G759" s="2" t="inlineStr">
@@ -52501,7 +52501,7 @@
       </c>
       <c r="F760" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G760" s="2" t="inlineStr">
@@ -52570,7 +52570,7 @@
       </c>
       <c r="F761" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G761" s="2" t="inlineStr">
@@ -66922,7 +66922,7 @@
       </c>
       <c r="F969" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G969" s="2" t="inlineStr">
@@ -66991,7 +66991,7 @@
       </c>
       <c r="F970" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G970" s="2" t="inlineStr">
@@ -67060,7 +67060,7 @@
       </c>
       <c r="F971" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G971" s="2" t="inlineStr">
@@ -67129,7 +67129,7 @@
       </c>
       <c r="F972" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G972" s="2" t="inlineStr">
@@ -67198,7 +67198,7 @@
       </c>
       <c r="F973" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G973" s="2" t="inlineStr">
@@ -69199,7 +69199,7 @@
       </c>
       <c r="F1002" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1002" s="2" t="inlineStr">
@@ -69268,7 +69268,7 @@
       </c>
       <c r="F1003" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1003" s="2" t="inlineStr">
@@ -69337,7 +69337,7 @@
       </c>
       <c r="F1004" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1004" s="2" t="inlineStr">
@@ -69406,7 +69406,7 @@
       </c>
       <c r="F1005" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1005" s="2" t="inlineStr">
@@ -69475,7 +69475,7 @@
       </c>
       <c r="F1006" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1006" s="2" t="inlineStr">
@@ -74167,7 +74167,7 @@
       </c>
       <c r="F1074" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1074" s="2" t="inlineStr">
@@ -74236,7 +74236,7 @@
       </c>
       <c r="F1075" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1075" s="2" t="inlineStr">
@@ -74305,7 +74305,7 @@
       </c>
       <c r="F1076" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1076" s="2" t="inlineStr">
@@ -74374,7 +74374,7 @@
       </c>
       <c r="F1077" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1077" s="2" t="inlineStr">
@@ -74443,7 +74443,7 @@
       </c>
       <c r="F1078" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1078" s="2" t="inlineStr">
@@ -84034,7 +84034,7 @@
       </c>
       <c r="F1217" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1217" s="2" t="inlineStr">
@@ -84103,7 +84103,7 @@
       </c>
       <c r="F1218" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1218" s="2" t="inlineStr">
@@ -84172,7 +84172,7 @@
       </c>
       <c r="F1219" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1219" s="2" t="inlineStr">
@@ -84241,7 +84241,7 @@
       </c>
       <c r="F1220" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1220" s="2" t="inlineStr">
@@ -84310,7 +84310,7 @@
       </c>
       <c r="F1221" s="2" t="inlineStr">
         <is>
-          <t>337 D SOBRAL DA SILVA REPRESENTACOES</t>
+          <t>D SOBRAL DA SILVA REPRESENTACOES</t>
         </is>
       </c>
       <c r="G1221" s="2" t="inlineStr">
@@ -84636,11 +84636,11 @@
         </is>
       </c>
       <c r="B1226" s="2" t="n">
-        <v>564822.0</v>
+        <v>564845.0</v>
       </c>
       <c r="C1226" s="2" t="inlineStr">
         <is>
-          <t>44860000341</t>
+          <t>44860010341</t>
         </is>
       </c>
       <c r="D1226" s="2" t="inlineStr">
@@ -84650,12 +84650,12 @@
       </c>
       <c r="E1226" s="2" t="inlineStr">
         <is>
-          <t>SPC</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1226" s="2" t="inlineStr">
         <is>
-          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
         </is>
       </c>
       <c r="G1226" s="2" t="inlineStr">
@@ -84674,19 +84674,19 @@
         </is>
       </c>
       <c r="J1226" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1226" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1226" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M1226" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N1226" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O1226" s="2" t="n">
         <v>1.0</v>
@@ -84695,7 +84695,7 @@
         <v>1.0</v>
       </c>
       <c r="Q1226" s="2" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="1227">
@@ -84705,26 +84705,26 @@
         </is>
       </c>
       <c r="B1227" s="2" t="n">
-        <v>564822.0</v>
+        <v>564845.0</v>
       </c>
       <c r="C1227" s="2" t="inlineStr">
         <is>
-          <t>44860004005</t>
+          <t>44860010411</t>
         </is>
       </c>
       <c r="D1227" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
         </is>
       </c>
       <c r="E1227" s="2" t="inlineStr">
         <is>
-          <t>SPC</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1227" s="2" t="inlineStr">
         <is>
-          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
         </is>
       </c>
       <c r="G1227" s="2" t="inlineStr">
@@ -84743,28 +84743,28 @@
         </is>
       </c>
       <c r="J1227" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1227" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1227" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M1227" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N1227" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O1227" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="P1227" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1227" s="2" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="1228">
@@ -84774,16 +84774,16 @@
         </is>
       </c>
       <c r="B1228" s="2" t="n">
-        <v>564845.0</v>
+        <v>564846.0</v>
       </c>
       <c r="C1228" s="2" t="inlineStr">
         <is>
-          <t>44860010341</t>
+          <t>43860000306</t>
         </is>
       </c>
       <c r="D1228" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
         </is>
       </c>
       <c r="E1228" s="2" t="inlineStr">
@@ -84798,7 +84798,7 @@
       </c>
       <c r="G1228" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H1228" s="2" t="inlineStr">
@@ -84843,16 +84843,16 @@
         </is>
       </c>
       <c r="B1229" s="2" t="n">
-        <v>564845.0</v>
+        <v>564847.0</v>
       </c>
       <c r="C1229" s="2" t="inlineStr">
         <is>
-          <t>44860010411</t>
+          <t>44860010341</t>
         </is>
       </c>
       <c r="D1229" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
         </is>
       </c>
       <c r="E1229" s="2" t="inlineStr">
@@ -84912,16 +84912,16 @@
         </is>
       </c>
       <c r="B1230" s="2" t="n">
-        <v>564846.0</v>
+        <v>564847.0</v>
       </c>
       <c r="C1230" s="2" t="inlineStr">
         <is>
-          <t>43860000306</t>
+          <t>44860010411</t>
         </is>
       </c>
       <c r="D1230" s="2" t="inlineStr">
         <is>
-          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
         </is>
       </c>
       <c r="E1230" s="2" t="inlineStr">
@@ -84936,7 +84936,7 @@
       </c>
       <c r="G1230" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1230" s="2" t="inlineStr">
@@ -84981,7 +84981,7 @@
         </is>
       </c>
       <c r="B1231" s="2" t="n">
-        <v>564847.0</v>
+        <v>564848.0</v>
       </c>
       <c r="C1231" s="2" t="inlineStr">
         <is>
@@ -85050,7 +85050,7 @@
         </is>
       </c>
       <c r="B1232" s="2" t="n">
-        <v>564847.0</v>
+        <v>564848.0</v>
       </c>
       <c r="C1232" s="2" t="inlineStr">
         <is>
@@ -85119,7 +85119,7 @@
         </is>
       </c>
       <c r="B1233" s="2" t="n">
-        <v>564848.0</v>
+        <v>564849.0</v>
       </c>
       <c r="C1233" s="2" t="inlineStr">
         <is>
@@ -85188,7 +85188,7 @@
         </is>
       </c>
       <c r="B1234" s="2" t="n">
-        <v>564848.0</v>
+        <v>564849.0</v>
       </c>
       <c r="C1234" s="2" t="inlineStr">
         <is>
@@ -85257,7 +85257,7 @@
         </is>
       </c>
       <c r="B1235" s="2" t="n">
-        <v>564849.0</v>
+        <v>564850.0</v>
       </c>
       <c r="C1235" s="2" t="inlineStr">
         <is>
@@ -85326,7 +85326,7 @@
         </is>
       </c>
       <c r="B1236" s="2" t="n">
-        <v>564849.0</v>
+        <v>564850.0</v>
       </c>
       <c r="C1236" s="2" t="inlineStr">
         <is>
@@ -85395,16 +85395,16 @@
         </is>
       </c>
       <c r="B1237" s="2" t="n">
-        <v>564850.0</v>
+        <v>564851.0</v>
       </c>
       <c r="C1237" s="2" t="inlineStr">
         <is>
-          <t>44860010341</t>
+          <t>43860000306</t>
         </is>
       </c>
       <c r="D1237" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
         </is>
       </c>
       <c r="E1237" s="2" t="inlineStr">
@@ -85419,7 +85419,7 @@
       </c>
       <c r="G1237" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H1237" s="2" t="inlineStr">
@@ -85464,16 +85464,16 @@
         </is>
       </c>
       <c r="B1238" s="2" t="n">
-        <v>564850.0</v>
+        <v>564852.0</v>
       </c>
       <c r="C1238" s="2" t="inlineStr">
         <is>
-          <t>44860010411</t>
+          <t>44860010341</t>
         </is>
       </c>
       <c r="D1238" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
         </is>
       </c>
       <c r="E1238" s="2" t="inlineStr">
@@ -85533,16 +85533,16 @@
         </is>
       </c>
       <c r="B1239" s="2" t="n">
-        <v>564851.0</v>
+        <v>564852.0</v>
       </c>
       <c r="C1239" s="2" t="inlineStr">
         <is>
-          <t>43860000306</t>
+          <t>44860010411</t>
         </is>
       </c>
       <c r="D1239" s="2" t="inlineStr">
         <is>
-          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
         </is>
       </c>
       <c r="E1239" s="2" t="inlineStr">
@@ -85557,7 +85557,7 @@
       </c>
       <c r="G1239" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1239" s="2" t="inlineStr">
@@ -85602,16 +85602,16 @@
         </is>
       </c>
       <c r="B1240" s="2" t="n">
-        <v>564852.0</v>
+        <v>564853.0</v>
       </c>
       <c r="C1240" s="2" t="inlineStr">
         <is>
-          <t>44860010341</t>
+          <t>43860000306</t>
         </is>
       </c>
       <c r="D1240" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
         </is>
       </c>
       <c r="E1240" s="2" t="inlineStr">
@@ -85626,7 +85626,7 @@
       </c>
       <c r="G1240" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H1240" s="2" t="inlineStr">
@@ -85671,16 +85671,16 @@
         </is>
       </c>
       <c r="B1241" s="2" t="n">
-        <v>564852.0</v>
+        <v>564854.0</v>
       </c>
       <c r="C1241" s="2" t="inlineStr">
         <is>
-          <t>44860010411</t>
+          <t>44860010341</t>
         </is>
       </c>
       <c r="D1241" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
         </is>
       </c>
       <c r="E1241" s="2" t="inlineStr">
@@ -85740,16 +85740,16 @@
         </is>
       </c>
       <c r="B1242" s="2" t="n">
-        <v>564853.0</v>
+        <v>564854.0</v>
       </c>
       <c r="C1242" s="2" t="inlineStr">
         <is>
-          <t>43860000306</t>
+          <t>44860010411</t>
         </is>
       </c>
       <c r="D1242" s="2" t="inlineStr">
         <is>
-          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
         </is>
       </c>
       <c r="E1242" s="2" t="inlineStr">
@@ -85764,7 +85764,7 @@
       </c>
       <c r="G1242" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1242" s="2" t="inlineStr">
@@ -85809,7 +85809,7 @@
         </is>
       </c>
       <c r="B1243" s="2" t="n">
-        <v>564854.0</v>
+        <v>564855.0</v>
       </c>
       <c r="C1243" s="2" t="inlineStr">
         <is>
@@ -85878,7 +85878,7 @@
         </is>
       </c>
       <c r="B1244" s="2" t="n">
-        <v>564854.0</v>
+        <v>564855.0</v>
       </c>
       <c r="C1244" s="2" t="inlineStr">
         <is>
@@ -85947,7 +85947,7 @@
         </is>
       </c>
       <c r="B1245" s="2" t="n">
-        <v>564855.0</v>
+        <v>564856.0</v>
       </c>
       <c r="C1245" s="2" t="inlineStr">
         <is>
@@ -86016,7 +86016,7 @@
         </is>
       </c>
       <c r="B1246" s="2" t="n">
-        <v>564855.0</v>
+        <v>564856.0</v>
       </c>
       <c r="C1246" s="2" t="inlineStr">
         <is>
@@ -86085,7 +86085,7 @@
         </is>
       </c>
       <c r="B1247" s="2" t="n">
-        <v>564856.0</v>
+        <v>564857.0</v>
       </c>
       <c r="C1247" s="2" t="inlineStr">
         <is>
@@ -86154,7 +86154,7 @@
         </is>
       </c>
       <c r="B1248" s="2" t="n">
-        <v>564856.0</v>
+        <v>564857.0</v>
       </c>
       <c r="C1248" s="2" t="inlineStr">
         <is>
@@ -86223,7 +86223,7 @@
         </is>
       </c>
       <c r="B1249" s="2" t="n">
-        <v>564857.0</v>
+        <v>564858.0</v>
       </c>
       <c r="C1249" s="2" t="inlineStr">
         <is>
@@ -86292,7 +86292,7 @@
         </is>
       </c>
       <c r="B1250" s="2" t="n">
-        <v>564857.0</v>
+        <v>564858.0</v>
       </c>
       <c r="C1250" s="2" t="inlineStr">
         <is>
@@ -86361,7 +86361,7 @@
         </is>
       </c>
       <c r="B1251" s="2" t="n">
-        <v>564858.0</v>
+        <v>564859.0</v>
       </c>
       <c r="C1251" s="2" t="inlineStr">
         <is>
@@ -86430,7 +86430,7 @@
         </is>
       </c>
       <c r="B1252" s="2" t="n">
-        <v>564858.0</v>
+        <v>564859.0</v>
       </c>
       <c r="C1252" s="2" t="inlineStr">
         <is>
@@ -86499,7 +86499,7 @@
         </is>
       </c>
       <c r="B1253" s="2" t="n">
-        <v>564859.0</v>
+        <v>564860.0</v>
       </c>
       <c r="C1253" s="2" t="inlineStr">
         <is>
@@ -86568,7 +86568,7 @@
         </is>
       </c>
       <c r="B1254" s="2" t="n">
-        <v>564859.0</v>
+        <v>564860.0</v>
       </c>
       <c r="C1254" s="2" t="inlineStr">
         <is>
@@ -86637,7 +86637,7 @@
         </is>
       </c>
       <c r="B1255" s="2" t="n">
-        <v>564860.0</v>
+        <v>564861.0</v>
       </c>
       <c r="C1255" s="2" t="inlineStr">
         <is>
@@ -86706,7 +86706,7 @@
         </is>
       </c>
       <c r="B1256" s="2" t="n">
-        <v>564860.0</v>
+        <v>564861.0</v>
       </c>
       <c r="C1256" s="2" t="inlineStr">
         <is>
@@ -86775,7 +86775,7 @@
         </is>
       </c>
       <c r="B1257" s="2" t="n">
-        <v>564861.0</v>
+        <v>564862.0</v>
       </c>
       <c r="C1257" s="2" t="inlineStr">
         <is>
@@ -86844,7 +86844,7 @@
         </is>
       </c>
       <c r="B1258" s="2" t="n">
-        <v>564861.0</v>
+        <v>564862.0</v>
       </c>
       <c r="C1258" s="2" t="inlineStr">
         <is>
@@ -86913,16 +86913,16 @@
         </is>
       </c>
       <c r="B1259" s="2" t="n">
-        <v>564862.0</v>
+        <v>564947.0</v>
       </c>
       <c r="C1259" s="2" t="inlineStr">
         <is>
-          <t>44860010341</t>
+          <t>08760000306</t>
         </is>
       </c>
       <c r="D1259" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
         </is>
       </c>
       <c r="E1259" s="2" t="inlineStr">
@@ -86932,12 +86932,12 @@
       </c>
       <c r="F1259" s="2" t="inlineStr">
         <is>
-          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+          <t>232 G L PEREIRA PINHEIRO</t>
         </is>
       </c>
       <c r="G1259" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H1259" s="2" t="inlineStr">
@@ -86957,19 +86957,19 @@
         <v>2.0</v>
       </c>
       <c r="L1259" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="M1259" s="2" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="N1259" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="O1259" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="P1259" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q1259" s="2" t="n">
         <v>12.0</v>
@@ -86982,16 +86982,16 @@
         </is>
       </c>
       <c r="B1260" s="2" t="n">
-        <v>564862.0</v>
+        <v>564947.0</v>
       </c>
       <c r="C1260" s="2" t="inlineStr">
         <is>
-          <t>44860010411</t>
+          <t>08760020306</t>
         </is>
       </c>
       <c r="D1260" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
         </is>
       </c>
       <c r="E1260" s="2" t="inlineStr">
@@ -87001,12 +87001,12 @@
       </c>
       <c r="F1260" s="2" t="inlineStr">
         <is>
-          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+          <t>232 G L PEREIRA PINHEIRO</t>
         </is>
       </c>
       <c r="G1260" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H1260" s="2" t="inlineStr">
@@ -87020,7 +87020,7 @@
         </is>
       </c>
       <c r="J1260" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K1260" s="2" t="n">
         <v>2.0</v>
@@ -87035,7 +87035,7 @@
         <v>2.0</v>
       </c>
       <c r="O1260" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P1260" s="2" t="n">
         <v>1.0</v>
@@ -87051,16 +87051,16 @@
         </is>
       </c>
       <c r="B1261" s="2" t="n">
-        <v>564947.0</v>
+        <v>564948.0</v>
       </c>
       <c r="C1261" s="2" t="inlineStr">
         <is>
-          <t>08760000306</t>
+          <t>44860010341</t>
         </is>
       </c>
       <c r="D1261" s="2" t="inlineStr">
         <is>
-          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
         </is>
       </c>
       <c r="E1261" s="2" t="inlineStr">
@@ -87075,7 +87075,7 @@
       </c>
       <c r="G1261" s="2" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1261" s="2" t="inlineStr">
@@ -87095,19 +87095,19 @@
         <v>2.0</v>
       </c>
       <c r="L1261" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M1261" s="2" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="N1261" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="O1261" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="P1261" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1261" s="2" t="n">
         <v>12.0</v>
@@ -87120,31 +87120,31 @@
         </is>
       </c>
       <c r="B1262" s="2" t="n">
-        <v>564947.0</v>
+        <v>564984.0</v>
       </c>
       <c r="C1262" s="2" t="inlineStr">
         <is>
-          <t>08760020306</t>
+          <t>44860004005</t>
         </is>
       </c>
       <c r="D1262" s="2" t="inlineStr">
         <is>
-          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
         </is>
       </c>
       <c r="E1262" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>REM</t>
         </is>
       </c>
       <c r="F1262" s="2" t="inlineStr">
         <is>
-          <t>232 G L PEREIRA PINHEIRO</t>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
         </is>
       </c>
       <c r="G1262" s="2" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1262" s="2" t="inlineStr">
@@ -87161,7 +87161,7 @@
         <v>1.0</v>
       </c>
       <c r="K1262" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1262" s="2" t="n">
         <v>2.0</v>
@@ -87176,7 +87176,7 @@
         <v>2.0</v>
       </c>
       <c r="P1262" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1262" s="2" t="n">
         <v>12.0</v>
@@ -87189,26 +87189,26 @@
         </is>
       </c>
       <c r="B1263" s="2" t="n">
-        <v>564948.0</v>
+        <v>564984.0</v>
       </c>
       <c r="C1263" s="2" t="inlineStr">
         <is>
-          <t>44860010341</t>
+          <t>44860010007</t>
         </is>
       </c>
       <c r="D1263" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
         </is>
       </c>
       <c r="E1263" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>REM</t>
         </is>
       </c>
       <c r="F1263" s="2" t="inlineStr">
         <is>
-          <t>232 G L PEREIRA PINHEIRO</t>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
         </is>
       </c>
       <c r="G1263" s="2" t="inlineStr">
@@ -87227,10 +87227,10 @@
         </is>
       </c>
       <c r="J1263" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K1263" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1263" s="2" t="n">
         <v>2.0</v>
@@ -87242,10 +87242,10 @@
         <v>2.0</v>
       </c>
       <c r="O1263" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P1263" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1263" s="2" t="n">
         <v>12.0</v>
@@ -87254,35 +87254,35 @@
     <row r="1264">
       <c r="A1264" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B1264" s="2" t="n">
-        <v>564984.0</v>
+        <v>565160.0</v>
       </c>
       <c r="C1264" s="2" t="inlineStr">
         <is>
-          <t>44860004005</t>
+          <t>43860000007</t>
         </is>
       </c>
       <c r="D1264" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
         </is>
       </c>
       <c r="E1264" s="2" t="inlineStr">
         <is>
-          <t>REM</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1264" s="2" t="inlineStr">
         <is>
-          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
         </is>
       </c>
       <c r="G1264" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H1264" s="2" t="inlineStr">
@@ -87299,7 +87299,7 @@
         <v>1.0</v>
       </c>
       <c r="K1264" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1264" s="2" t="n">
         <v>2.0</v>
@@ -87314,7 +87314,7 @@
         <v>2.0</v>
       </c>
       <c r="P1264" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1264" s="2" t="n">
         <v>12.0</v>
@@ -87323,30 +87323,30 @@
     <row r="1265">
       <c r="A1265" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="B1265" s="2" t="n">
-        <v>564984.0</v>
+        <v>565161.0</v>
       </c>
       <c r="C1265" s="2" t="inlineStr">
         <is>
-          <t>44860010007</t>
+          <t>44860004005</t>
         </is>
       </c>
       <c r="D1265" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
         </is>
       </c>
       <c r="E1265" s="2" t="inlineStr">
         <is>
-          <t>REM</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1265" s="2" t="inlineStr">
         <is>
-          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
         </is>
       </c>
       <c r="G1265" s="2" t="inlineStr">
@@ -87368,7 +87368,7 @@
         <v>1.0</v>
       </c>
       <c r="K1265" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1265" s="2" t="n">
         <v>2.0</v>
@@ -87383,7 +87383,7 @@
         <v>2.0</v>
       </c>
       <c r="P1265" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1265" s="2" t="n">
         <v>12.0</v>
@@ -87396,16 +87396,16 @@
         </is>
       </c>
       <c r="B1266" s="2" t="n">
-        <v>565160.0</v>
+        <v>565161.0</v>
       </c>
       <c r="C1266" s="2" t="inlineStr">
         <is>
-          <t>43860000007</t>
+          <t>44860010007</t>
         </is>
       </c>
       <c r="D1266" s="2" t="inlineStr">
         <is>
-          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
         </is>
       </c>
       <c r="E1266" s="2" t="inlineStr">
@@ -87420,7 +87420,7 @@
       </c>
       <c r="G1266" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1266" s="2" t="inlineStr">
@@ -87465,26 +87465,26 @@
         </is>
       </c>
       <c r="B1267" s="2" t="n">
-        <v>565161.0</v>
+        <v>565185.0</v>
       </c>
       <c r="C1267" s="2" t="inlineStr">
         <is>
-          <t>44860004005</t>
+          <t>44860010007</t>
         </is>
       </c>
       <c r="D1267" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
         </is>
       </c>
       <c r="E1267" s="2" t="inlineStr">
         <is>
-          <t>CENTRO OESTE</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1267" s="2" t="inlineStr">
         <is>
-          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+          <t>232 G L PEREIRA PINHEIRO</t>
         </is>
       </c>
       <c r="G1267" s="2" t="inlineStr">
@@ -87534,26 +87534,26 @@
         </is>
       </c>
       <c r="B1268" s="2" t="n">
-        <v>565161.0</v>
+        <v>565185.0</v>
       </c>
       <c r="C1268" s="2" t="inlineStr">
         <is>
-          <t>44860010007</t>
+          <t>44860010341</t>
         </is>
       </c>
       <c r="D1268" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
         </is>
       </c>
       <c r="E1268" s="2" t="inlineStr">
         <is>
-          <t>CENTRO OESTE</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1268" s="2" t="inlineStr">
         <is>
-          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+          <t>232 G L PEREIRA PINHEIRO</t>
         </is>
       </c>
       <c r="G1268" s="2" t="inlineStr">
@@ -87603,16 +87603,16 @@
         </is>
       </c>
       <c r="B1269" s="2" t="n">
-        <v>565185.0</v>
+        <v>565194.0</v>
       </c>
       <c r="C1269" s="2" t="inlineStr">
         <is>
-          <t>44860010007</t>
+          <t>08760000306</t>
         </is>
       </c>
       <c r="D1269" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
         </is>
       </c>
       <c r="E1269" s="2" t="inlineStr">
@@ -87627,7 +87627,7 @@
       </c>
       <c r="G1269" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H1269" s="2" t="inlineStr">
@@ -87672,16 +87672,16 @@
         </is>
       </c>
       <c r="B1270" s="2" t="n">
-        <v>565185.0</v>
+        <v>565194.0</v>
       </c>
       <c r="C1270" s="2" t="inlineStr">
         <is>
-          <t>44860010341</t>
+          <t>08760020007</t>
         </is>
       </c>
       <c r="D1270" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
         </is>
       </c>
       <c r="E1270" s="2" t="inlineStr">
@@ -87696,7 +87696,7 @@
       </c>
       <c r="G1270" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H1270" s="2" t="inlineStr">
@@ -87741,11 +87741,11 @@
         </is>
       </c>
       <c r="B1271" s="2" t="n">
-        <v>565194.0</v>
+        <v>565214.0</v>
       </c>
       <c r="C1271" s="2" t="inlineStr">
         <is>
-          <t>08760000306</t>
+          <t>08760020306</t>
         </is>
       </c>
       <c r="D1271" s="2" t="inlineStr">
@@ -87755,12 +87755,12 @@
       </c>
       <c r="E1271" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1271" s="2" t="inlineStr">
         <is>
-          <t>232 G L PEREIRA PINHEIRO</t>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
         </is>
       </c>
       <c r="G1271" s="2" t="inlineStr">
@@ -87782,7 +87782,7 @@
         <v>1.0</v>
       </c>
       <c r="K1271" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1271" s="2" t="n">
         <v>2.0</v>
@@ -87797,7 +87797,7 @@
         <v>2.0</v>
       </c>
       <c r="P1271" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1271" s="2" t="n">
         <v>12.0</v>
@@ -87810,31 +87810,31 @@
         </is>
       </c>
       <c r="B1272" s="2" t="n">
-        <v>565194.0</v>
+        <v>565215.0</v>
       </c>
       <c r="C1272" s="2" t="inlineStr">
         <is>
-          <t>08760020007</t>
+          <t>44860004005</t>
         </is>
       </c>
       <c r="D1272" s="2" t="inlineStr">
         <is>
-          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
         </is>
       </c>
       <c r="E1272" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>CENTRO OESTE</t>
         </is>
       </c>
       <c r="F1272" s="2" t="inlineStr">
         <is>
-          <t>232 G L PEREIRA PINHEIRO</t>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
         </is>
       </c>
       <c r="G1272" s="2" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1272" s="2" t="inlineStr">
@@ -87848,7 +87848,7 @@
         </is>
       </c>
       <c r="J1272" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1272" s="2" t="n">
         <v>2.0</v>
@@ -87863,7 +87863,7 @@
         <v>2.0</v>
       </c>
       <c r="O1272" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P1272" s="2" t="n">
         <v>1.0</v>
@@ -87879,11 +87879,11 @@
         </is>
       </c>
       <c r="B1273" s="2" t="n">
-        <v>565214.0</v>
+        <v>565216.0</v>
       </c>
       <c r="C1273" s="2" t="inlineStr">
         <is>
-          <t>08760020306</t>
+          <t>08760000306</t>
         </is>
       </c>
       <c r="D1273" s="2" t="inlineStr">
@@ -87893,12 +87893,12 @@
       </c>
       <c r="E1273" s="2" t="inlineStr">
         <is>
-          <t>CENTRO OESTE</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1273" s="2" t="inlineStr">
         <is>
-          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+          <t>240 RAMON MAIA DE LIMA</t>
         </is>
       </c>
       <c r="G1273" s="2" t="inlineStr">
@@ -87948,26 +87948,26 @@
         </is>
       </c>
       <c r="B1274" s="2" t="n">
-        <v>565215.0</v>
+        <v>565217.0</v>
       </c>
       <c r="C1274" s="2" t="inlineStr">
         <is>
-          <t>44860004005</t>
+          <t>44860010341</t>
         </is>
       </c>
       <c r="D1274" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
         </is>
       </c>
       <c r="E1274" s="2" t="inlineStr">
         <is>
-          <t>CENTRO OESTE</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1274" s="2" t="inlineStr">
         <is>
-          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+          <t>240 RAMON MAIA DE LIMA</t>
         </is>
       </c>
       <c r="G1274" s="2" t="inlineStr">
@@ -87986,10 +87986,10 @@
         </is>
       </c>
       <c r="J1274" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K1274" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1274" s="2" t="n">
         <v>2.0</v>
@@ -88001,10 +88001,10 @@
         <v>2.0</v>
       </c>
       <c r="O1274" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P1274" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1274" s="2" t="n">
         <v>12.0</v>
@@ -88017,16 +88017,16 @@
         </is>
       </c>
       <c r="B1275" s="2" t="n">
-        <v>565216.0</v>
+        <v>565217.0</v>
       </c>
       <c r="C1275" s="2" t="inlineStr">
         <is>
-          <t>08760000306</t>
+          <t>44860013330</t>
         </is>
       </c>
       <c r="D1275" s="2" t="inlineStr">
         <is>
-          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC MARFIM/OURO</t>
         </is>
       </c>
       <c r="E1275" s="2" t="inlineStr">
@@ -88041,7 +88041,7 @@
       </c>
       <c r="G1275" s="2" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1275" s="2" t="inlineStr">
@@ -88086,16 +88086,16 @@
         </is>
       </c>
       <c r="B1276" s="2" t="n">
-        <v>565217.0</v>
+        <v>565242.0</v>
       </c>
       <c r="C1276" s="2" t="inlineStr">
         <is>
-          <t>44860010341</t>
+          <t>44860004005</t>
         </is>
       </c>
       <c r="D1276" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
         </is>
       </c>
       <c r="E1276" s="2" t="inlineStr">
@@ -88105,7 +88105,7 @@
       </c>
       <c r="F1276" s="2" t="inlineStr">
         <is>
-          <t>240 RAMON MAIA DE LIMA</t>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
         </is>
       </c>
       <c r="G1276" s="2" t="inlineStr">
@@ -88124,10 +88124,10 @@
         </is>
       </c>
       <c r="J1276" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1276" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1276" s="2" t="n">
         <v>2.0</v>
@@ -88139,10 +88139,10 @@
         <v>2.0</v>
       </c>
       <c r="O1276" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P1276" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1276" s="2" t="n">
         <v>12.0</v>
@@ -88155,16 +88155,16 @@
         </is>
       </c>
       <c r="B1277" s="2" t="n">
-        <v>565217.0</v>
+        <v>565242.0</v>
       </c>
       <c r="C1277" s="2" t="inlineStr">
         <is>
-          <t>44860013330</t>
+          <t>44860010007</t>
         </is>
       </c>
       <c r="D1277" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC MARFIM/OURO</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
         </is>
       </c>
       <c r="E1277" s="2" t="inlineStr">
@@ -88174,7 +88174,7 @@
       </c>
       <c r="F1277" s="2" t="inlineStr">
         <is>
-          <t>240 RAMON MAIA DE LIMA</t>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
         </is>
       </c>
       <c r="G1277" s="2" t="inlineStr">
@@ -88193,10 +88193,10 @@
         </is>
       </c>
       <c r="J1277" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1277" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1277" s="2" t="n">
         <v>2.0</v>
@@ -88208,10 +88208,10 @@
         <v>2.0</v>
       </c>
       <c r="O1277" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P1277" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1277" s="2" t="n">
         <v>12.0</v>
@@ -88228,7 +88228,7 @@
       </c>
       <c r="C1278" s="2" t="inlineStr">
         <is>
-          <t>44860004005</t>
+          <t>44860014005</t>
         </is>
       </c>
       <c r="D1278" s="2" t="inlineStr">
@@ -88293,16 +88293,16 @@
         </is>
       </c>
       <c r="B1279" s="2" t="n">
-        <v>565242.0</v>
+        <v>565243.0</v>
       </c>
       <c r="C1279" s="2" t="inlineStr">
         <is>
-          <t>44860010007</t>
+          <t>43860000306</t>
         </is>
       </c>
       <c r="D1279" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
         </is>
       </c>
       <c r="E1279" s="2" t="inlineStr">
@@ -88317,7 +88317,7 @@
       </c>
       <c r="G1279" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H1279" s="2" t="inlineStr">
@@ -88362,26 +88362,26 @@
         </is>
       </c>
       <c r="B1280" s="2" t="n">
-        <v>565242.0</v>
+        <v>565309.0</v>
       </c>
       <c r="C1280" s="2" t="inlineStr">
         <is>
-          <t>44860014005</t>
+          <t>44860000341</t>
         </is>
       </c>
       <c r="D1280" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
         </is>
       </c>
       <c r="E1280" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>SPC</t>
         </is>
       </c>
       <c r="F1280" s="2" t="inlineStr">
         <is>
-          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+          <t>39 C A VELOSO REPRESENTAÇÕES</t>
         </is>
       </c>
       <c r="G1280" s="2" t="inlineStr">
@@ -88400,19 +88400,19 @@
         </is>
       </c>
       <c r="J1280" s="2" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K1280" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1280" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M1280" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N1280" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O1280" s="2" t="n">
         <v>1.0</v>
@@ -88421,7 +88421,7 @@
         <v>1.0</v>
       </c>
       <c r="Q1280" s="2" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="1281">
@@ -88431,31 +88431,31 @@
         </is>
       </c>
       <c r="B1281" s="2" t="n">
-        <v>565243.0</v>
+        <v>565309.0</v>
       </c>
       <c r="C1281" s="2" t="inlineStr">
         <is>
-          <t>43860000306</t>
+          <t>44860004005</t>
         </is>
       </c>
       <c r="D1281" s="2" t="inlineStr">
         <is>
-          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
         </is>
       </c>
       <c r="E1281" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>SPC</t>
         </is>
       </c>
       <c r="F1281" s="2" t="inlineStr">
         <is>
-          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+          <t>39 C A VELOSO REPRESENTAÇÕES</t>
         </is>
       </c>
       <c r="G1281" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1281" s="2" t="inlineStr">
@@ -88469,28 +88469,28 @@
         </is>
       </c>
       <c r="J1281" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K1281" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1281" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="M1281" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N1281" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O1281" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="P1281" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q1281" s="2" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="1282">
@@ -88500,26 +88500,26 @@
         </is>
       </c>
       <c r="B1282" s="2" t="n">
-        <v>565309.0</v>
+        <v>565331.0</v>
       </c>
       <c r="C1282" s="2" t="inlineStr">
         <is>
-          <t>44860000341</t>
+          <t>44860000007</t>
         </is>
       </c>
       <c r="D1282" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
         </is>
       </c>
       <c r="E1282" s="2" t="inlineStr">
         <is>
-          <t>SPC</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1282" s="2" t="inlineStr">
         <is>
-          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
         </is>
       </c>
       <c r="G1282" s="2" t="inlineStr">
@@ -88538,28 +88538,28 @@
         </is>
       </c>
       <c r="J1282" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K1282" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="L1282" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M1282" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N1282" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O1282" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P1282" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1282" s="2" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="1283">
@@ -88569,26 +88569,26 @@
         </is>
       </c>
       <c r="B1283" s="2" t="n">
-        <v>565309.0</v>
+        <v>565331.0</v>
       </c>
       <c r="C1283" s="2" t="inlineStr">
         <is>
-          <t>44860004005</t>
+          <t>44860010411</t>
         </is>
       </c>
       <c r="D1283" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
         </is>
       </c>
       <c r="E1283" s="2" t="inlineStr">
         <is>
-          <t>SPC</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1283" s="2" t="inlineStr">
         <is>
-          <t>39 C A VELOSO REPRESENTAÇÕES</t>
+          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
         </is>
       </c>
       <c r="G1283" s="2" t="inlineStr">
@@ -88613,22 +88613,22 @@
         <v>1.0</v>
       </c>
       <c r="L1283" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="M1283" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="N1283" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O1283" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P1283" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1283" s="2" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="1284">
@@ -88638,16 +88638,16 @@
         </is>
       </c>
       <c r="B1284" s="2" t="n">
-        <v>565331.0</v>
+        <v>565332.0</v>
       </c>
       <c r="C1284" s="2" t="inlineStr">
         <is>
-          <t>44860000007</t>
+          <t>43860010411</t>
         </is>
       </c>
       <c r="D1284" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
         </is>
       </c>
       <c r="E1284" s="2" t="inlineStr">
@@ -88662,7 +88662,7 @@
       </c>
       <c r="G1284" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>438</t>
         </is>
       </c>
       <c r="H1284" s="2" t="inlineStr">
@@ -88676,10 +88676,10 @@
         </is>
       </c>
       <c r="J1284" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1284" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1284" s="2" t="n">
         <v>2.0</v>
@@ -88691,10 +88691,10 @@
         <v>2.0</v>
       </c>
       <c r="O1284" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P1284" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1284" s="2" t="n">
         <v>12.0</v>
@@ -88707,16 +88707,16 @@
         </is>
       </c>
       <c r="B1285" s="2" t="n">
-        <v>565331.0</v>
+        <v>565345.0</v>
       </c>
       <c r="C1285" s="2" t="inlineStr">
         <is>
-          <t>44860010411</t>
+          <t>44860000007</t>
         </is>
       </c>
       <c r="D1285" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
         </is>
       </c>
       <c r="E1285" s="2" t="inlineStr">
@@ -88726,7 +88726,7 @@
       </c>
       <c r="F1285" s="2" t="inlineStr">
         <is>
-          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
         </is>
       </c>
       <c r="G1285" s="2" t="inlineStr">
@@ -88745,10 +88745,10 @@
         </is>
       </c>
       <c r="J1285" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1285" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1285" s="2" t="n">
         <v>2.0</v>
@@ -88760,10 +88760,10 @@
         <v>2.0</v>
       </c>
       <c r="O1285" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P1285" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q1285" s="2" t="n">
         <v>12.0</v>
@@ -88776,16 +88776,16 @@
         </is>
       </c>
       <c r="B1286" s="2" t="n">
-        <v>565332.0</v>
+        <v>565346.0</v>
       </c>
       <c r="C1286" s="2" t="inlineStr">
         <is>
-          <t>43860010411</t>
+          <t>08760020306</t>
         </is>
       </c>
       <c r="D1286" s="2" t="inlineStr">
         <is>
-          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
         </is>
       </c>
       <c r="E1286" s="2" t="inlineStr">
@@ -88795,12 +88795,12 @@
       </c>
       <c r="F1286" s="2" t="inlineStr">
         <is>
-          <t>194 WALLACE SHOES REPRESENTAÇOES</t>
+          <t>31 MARCOS VINICIO REPRES. LTDA</t>
         </is>
       </c>
       <c r="G1286" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H1286" s="2" t="inlineStr">
@@ -88845,7 +88845,7 @@
         </is>
       </c>
       <c r="B1287" s="2" t="n">
-        <v>565345.0</v>
+        <v>565352.0</v>
       </c>
       <c r="C1287" s="2" t="inlineStr">
         <is>
@@ -88859,12 +88859,12 @@
       </c>
       <c r="E1287" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>REM</t>
         </is>
       </c>
       <c r="F1287" s="2" t="inlineStr">
         <is>
-          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
         </is>
       </c>
       <c r="G1287" s="2" t="inlineStr">
@@ -88883,10 +88883,10 @@
         </is>
       </c>
       <c r="J1287" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K1287" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1287" s="2" t="n">
         <v>2.0</v>
@@ -88898,10 +88898,10 @@
         <v>2.0</v>
       </c>
       <c r="O1287" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P1287" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1287" s="2" t="n">
         <v>12.0</v>
@@ -88914,31 +88914,31 @@
         </is>
       </c>
       <c r="B1288" s="2" t="n">
-        <v>565346.0</v>
+        <v>565352.0</v>
       </c>
       <c r="C1288" s="2" t="inlineStr">
         <is>
-          <t>08760020306</t>
+          <t>44860004005</t>
         </is>
       </c>
       <c r="D1288" s="2" t="inlineStr">
         <is>
-          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
         </is>
       </c>
       <c r="E1288" s="2" t="inlineStr">
         <is>
-          <t>NORTE/NORDESTE</t>
+          <t>REM</t>
         </is>
       </c>
       <c r="F1288" s="2" t="inlineStr">
         <is>
-          <t>31 MARCOS VINICIO REPRES. LTDA</t>
+          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
         </is>
       </c>
       <c r="G1288" s="2" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H1288" s="2" t="inlineStr">
@@ -88952,10 +88952,10 @@
         </is>
       </c>
       <c r="J1288" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K1288" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1288" s="2" t="n">
         <v>2.0</v>
@@ -88967,10 +88967,10 @@
         <v>2.0</v>
       </c>
       <c r="O1288" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P1288" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q1288" s="2" t="n">
         <v>12.0</v>
@@ -88983,16 +88983,16 @@
         </is>
       </c>
       <c r="B1289" s="2" t="n">
-        <v>565352.0</v>
+        <v>565353.0</v>
       </c>
       <c r="C1289" s="2" t="inlineStr">
         <is>
-          <t>44860000007</t>
+          <t>08760000306</t>
         </is>
       </c>
       <c r="D1289" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
         </is>
       </c>
       <c r="E1289" s="2" t="inlineStr">
@@ -89007,7 +89007,7 @@
       </c>
       <c r="G1289" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>087</t>
         </is>
       </c>
       <c r="H1289" s="2" t="inlineStr">
@@ -89052,26 +89052,26 @@
         </is>
       </c>
       <c r="B1290" s="2" t="n">
-        <v>565352.0</v>
+        <v>565389.0</v>
       </c>
       <c r="C1290" s="2" t="inlineStr">
         <is>
-          <t>44860004005</t>
+          <t>44860003330</t>
         </is>
       </c>
       <c r="D1290" s="2" t="inlineStr">
         <is>
-          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+          <t>TENIS K360 ESTILO RESPITEC MARFIM/OURO</t>
         </is>
       </c>
       <c r="E1290" s="2" t="inlineStr">
         <is>
-          <t>REM</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="F1290" s="2" t="inlineStr">
         <is>
-          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+          <t>197 FABRICIO RIZZATO RODRIGUES</t>
         </is>
       </c>
       <c r="G1290" s="2" t="inlineStr">
@@ -89093,7 +89093,7 @@
         <v>1.0</v>
       </c>
       <c r="K1290" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1290" s="2" t="n">
         <v>2.0</v>
@@ -89102,7 +89102,7 @@
         <v>2.0</v>
       </c>
       <c r="N1290" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O1290" s="2" t="n">
         <v>2.0</v>
@@ -89121,31 +89121,31 @@
         </is>
       </c>
       <c r="B1291" s="2" t="n">
-        <v>565353.0</v>
+        <v>565390.0</v>
       </c>
       <c r="C1291" s="2" t="inlineStr">
         <is>
-          <t>08760000306</t>
+          <t>45560000017</t>
         </is>
       </c>
       <c r="D1291" s="2" t="inlineStr">
         <is>
-          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+          <t>TENIS K360 RETRO BRANCO/ROSA</t>
         </is>
       </c>
       <c r="E1291" s="2" t="inlineStr">
         <is>
-          <t>REM</t>
+          <t>SPI</t>
         </is>
       </c>
       <c r="F1291" s="2" t="inlineStr">
         <is>
-          <t>299 REPRESENTACOES JAMIR MACIEL ASSIS LTDA</t>
+          <t>197 FABRICIO RIZZATO RODRIGUES</t>
         </is>
       </c>
       <c r="G1291" s="2" t="inlineStr">
         <is>
-          <t>087</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H1291" s="2" t="inlineStr">
@@ -89159,19 +89159,19 @@
         </is>
       </c>
       <c r="J1291" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K1291" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="L1291" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="M1291" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="N1291" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O1291" s="2" t="n">
         <v>2.0</v>
@@ -89186,11 +89186,11 @@
     <row r="1292">
       <c r="A1292" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B1292" s="2" t="n">
-        <v>565389.0</v>
+        <v>565416.0</v>
       </c>
       <c r="C1292" s="2" t="inlineStr">
         <is>
@@ -89204,12 +89204,12 @@
       </c>
       <c r="E1292" s="2" t="inlineStr">
         <is>
-          <t>SPI</t>
+          <t>NORTE/NORDESTE</t>
         </is>
       </c>
       <c r="F1292" s="2" t="inlineStr">
         <is>
-          <t>197 FABRICIO RIZZATO RODRIGUES</t>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
         </is>
       </c>
       <c r="G1292" s="2" t="inlineStr">
@@ -89231,7 +89231,7 @@
         <v>1.0</v>
       </c>
       <c r="K1292" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="L1292" s="2" t="n">
         <v>2.0</v>
@@ -89240,7 +89240,7 @@
         <v>2.0</v>
       </c>
       <c r="N1292" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="O1292" s="2" t="n">
         <v>2.0</v>
@@ -89255,69 +89255,3726 @@
     <row r="1293">
       <c r="A1293" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B1293" s="2" t="n">
-        <v>565390.0</v>
+        <v>565416.0</v>
       </c>
       <c r="C1293" s="2" t="inlineStr">
         <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1293" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1293" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1293" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1293" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1293" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1293" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1293" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1293" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1293" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1293" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1294" s="2" t="n">
+        <v>565417.0</v>
+      </c>
+      <c r="C1294" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1294" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1294" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1294" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1294" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1294" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1294" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1294" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1294" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1294" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1294" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1294" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1294" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1294" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1294" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1295" s="2" t="n">
+        <v>565418.0</v>
+      </c>
+      <c r="C1295" s="2" t="inlineStr">
+        <is>
+          <t>43860000017</t>
+        </is>
+      </c>
+      <c r="D1295" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1295" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1295" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1295" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1295" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1295" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1295" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1295" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1295" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1295" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1295" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1295" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1295" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1295" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1296" s="2" t="n">
+        <v>565418.0</v>
+      </c>
+      <c r="C1296" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1296" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1296" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1296" s="2" t="inlineStr">
+        <is>
+          <t>267 F N CAMPELO REPRESENTACOES LTDA ­ ME</t>
+        </is>
+      </c>
+      <c r="G1296" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1296" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1296" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1296" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1296" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1296" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1296" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1296" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1296" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1296" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1296" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1297" s="2" t="n">
+        <v>565441.0</v>
+      </c>
+      <c r="C1297" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1297" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1297" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1297" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1297" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1297" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1297" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1297" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1297" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1297" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1297" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1297" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1297" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1297" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1297" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1298" s="2" t="n">
+        <v>565441.0</v>
+      </c>
+      <c r="C1298" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1298" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1298" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1298" s="2" t="inlineStr">
+        <is>
+          <t>11 GEORGE BORGES REPRESENTACOES EIRELI - ME</t>
+        </is>
+      </c>
+      <c r="G1298" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1298" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1298" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1298" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1298" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1298" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1298" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1298" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1298" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1298" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1298" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1299" s="2" t="n">
+        <v>565462.0</v>
+      </c>
+      <c r="C1299" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1299" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1299" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F1299" s="2" t="inlineStr">
+        <is>
+          <t>273 GLAUCIANE APARECIDA BERNARDES</t>
+        </is>
+      </c>
+      <c r="G1299" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1299" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1299" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1299" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1299" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1299" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1299" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1299" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1299" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1299" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1299" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1300" s="2" t="n">
+        <v>565462.0</v>
+      </c>
+      <c r="C1300" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1300" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1300" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F1300" s="2" t="inlineStr">
+        <is>
+          <t>273 GLAUCIANE APARECIDA BERNARDES</t>
+        </is>
+      </c>
+      <c r="G1300" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1300" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1300" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1300" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1300" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1300" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1300" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1300" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1300" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1300" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1300" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1301" s="2" t="n">
+        <v>565462.0</v>
+      </c>
+      <c r="C1301" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1301" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1301" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F1301" s="2" t="inlineStr">
+        <is>
+          <t>273 GLAUCIANE APARECIDA BERNARDES</t>
+        </is>
+      </c>
+      <c r="G1301" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1301" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1301" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1301" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1301" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1301" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1301" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1301" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1301" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1301" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1301" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1302" s="2" t="n">
+        <v>565463.0</v>
+      </c>
+      <c r="C1302" s="2" t="inlineStr">
+        <is>
+          <t>08760014005</t>
+        </is>
+      </c>
+      <c r="D1302" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE NUDE</t>
+        </is>
+      </c>
+      <c r="E1302" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F1302" s="2" t="inlineStr">
+        <is>
+          <t>273 GLAUCIANE APARECIDA BERNARDES</t>
+        </is>
+      </c>
+      <c r="G1302" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1302" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1302" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1302" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1302" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1302" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1302" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1302" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1302" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1302" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1302" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1303" s="2" t="n">
+        <v>565463.0</v>
+      </c>
+      <c r="C1303" s="2" t="inlineStr">
+        <is>
+          <t>08760020008</t>
+        </is>
+      </c>
+      <c r="D1303" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE ROSA</t>
+        </is>
+      </c>
+      <c r="E1303" s="2" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="F1303" s="2" t="inlineStr">
+        <is>
+          <t>273 GLAUCIANE APARECIDA BERNARDES</t>
+        </is>
+      </c>
+      <c r="G1303" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1303" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1303" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1303" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K1303" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1303" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1303" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1303" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1303" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1303" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1303" s="2" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1304" s="2" t="n">
+        <v>565490.0</v>
+      </c>
+      <c r="C1304" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1304" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1304" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1304" s="2" t="inlineStr">
+        <is>
+          <t>297 REPRESENTACAO JONATAS LTDA</t>
+        </is>
+      </c>
+      <c r="G1304" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1304" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1304" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1304" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1304" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1304" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1304" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="N1304" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="O1304" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="P1304" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="Q1304" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1305" s="2" t="n">
+        <v>565490.0</v>
+      </c>
+      <c r="C1305" s="2" t="inlineStr">
+        <is>
+          <t>44860010341</t>
+        </is>
+      </c>
+      <c r="D1305" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC BRANCO/PRATA</t>
+        </is>
+      </c>
+      <c r="E1305" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1305" s="2" t="inlineStr">
+        <is>
+          <t>297 REPRESENTACAO JONATAS LTDA</t>
+        </is>
+      </c>
+      <c r="G1305" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1305" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1305" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1305" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1305" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1305" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1305" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="N1305" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="O1305" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="P1305" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="Q1305" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1306" s="2" t="n">
+        <v>565491.0</v>
+      </c>
+      <c r="C1306" s="2" t="inlineStr">
+        <is>
+          <t>45560000007</t>
+        </is>
+      </c>
+      <c r="D1306" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO PRETO</t>
+        </is>
+      </c>
+      <c r="E1306" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1306" s="2" t="inlineStr">
+        <is>
+          <t>297 REPRESENTACAO JONATAS LTDA</t>
+        </is>
+      </c>
+      <c r="G1306" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1306" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1306" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1306" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1306" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1306" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1306" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="N1306" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="O1306" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="P1306" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="Q1306" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1307" s="2" t="n">
+        <v>565491.0</v>
+      </c>
+      <c r="C1307" s="2" t="inlineStr">
+        <is>
           <t>45560000017</t>
         </is>
       </c>
-      <c r="D1293" s="2" t="inlineStr">
+      <c r="D1307" s="2" t="inlineStr">
         <is>
           <t>TENIS K360 RETRO BRANCO/ROSA</t>
         </is>
       </c>
-      <c r="E1293" s="2" t="inlineStr">
+      <c r="E1307" s="2" t="inlineStr">
         <is>
           <t>SPI</t>
         </is>
       </c>
-      <c r="F1293" s="2" t="inlineStr">
-        <is>
-          <t>197 FABRICIO RIZZATO RODRIGUES</t>
-        </is>
-      </c>
-      <c r="G1293" s="2" t="inlineStr">
+      <c r="F1307" s="2" t="inlineStr">
+        <is>
+          <t>297 REPRESENTACAO JONATAS LTDA</t>
+        </is>
+      </c>
+      <c r="G1307" s="2" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
-      <c r="H1293" s="2" t="inlineStr">
-        <is>
-          <t>ABERTO</t>
-        </is>
-      </c>
-      <c r="I1293" s="2" t="inlineStr">
-        <is>
-          <t>PRODUÇÃO</t>
-        </is>
-      </c>
-      <c r="J1293" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K1293" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="L1293" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="M1293" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N1293" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="O1293" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="P1293" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Q1293" s="2" t="n">
+      <c r="H1307" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1307" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1307" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1307" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1307" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1307" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="N1307" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="O1307" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="P1307" s="2" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="Q1307" s="2" t="n">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1308" s="2" t="n">
+        <v>565491.0</v>
+      </c>
+      <c r="C1308" s="2" t="inlineStr">
+        <is>
+          <t>45560003330</t>
+        </is>
+      </c>
+      <c r="D1308" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO MARFIM/OURO</t>
+        </is>
+      </c>
+      <c r="E1308" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1308" s="2" t="inlineStr">
+        <is>
+          <t>297 REPRESENTACAO JONATAS LTDA</t>
+        </is>
+      </c>
+      <c r="G1308" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1308" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1308" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1308" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1308" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1308" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1308" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1308" s="2" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="O1308" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1308" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1308" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1309" s="2" t="n">
+        <v>565515.0</v>
+      </c>
+      <c r="C1309" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1309" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1309" s="2" t="inlineStr">
+        <is>
+          <t>SPI</t>
+        </is>
+      </c>
+      <c r="F1309" s="2" t="inlineStr">
+        <is>
+          <t>19 HAMILTON BIRIGUI REPRES. LTDA</t>
+        </is>
+      </c>
+      <c r="G1309" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1309" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1309" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1309" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1309" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1309" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1309" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1309" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1309" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1309" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1309" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1310" s="2" t="n">
+        <v>565590.0</v>
+      </c>
+      <c r="C1310" s="2" t="inlineStr">
+        <is>
+          <t>08760000306</t>
+        </is>
+      </c>
+      <c r="D1310" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1310" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1310" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1310" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1310" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1310" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1310" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1310" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1310" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1310" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1310" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1310" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1310" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1310" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1311" s="2" t="n">
+        <v>565590.0</v>
+      </c>
+      <c r="C1311" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1311" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1311" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1311" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1311" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1311" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1311" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1311" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1311" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1311" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1311" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1311" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1311" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1311" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1311" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1312" s="2" t="n">
+        <v>565591.0</v>
+      </c>
+      <c r="C1312" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1312" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1312" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1312" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1312" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1312" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1312" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1312" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1312" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1312" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1312" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1312" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1312" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1312" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1312" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1313" s="2" t="n">
+        <v>565591.0</v>
+      </c>
+      <c r="C1313" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1313" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1313" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1313" s="2" t="inlineStr">
+        <is>
+          <t>232 G L PEREIRA PINHEIRO</t>
+        </is>
+      </c>
+      <c r="G1313" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1313" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1313" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1313" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1313" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1313" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1313" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1313" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1313" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1313" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1313" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1314" s="2" t="n">
+        <v>565606.0</v>
+      </c>
+      <c r="C1314" s="2" t="inlineStr">
+        <is>
+          <t>44860000411</t>
+        </is>
+      </c>
+      <c r="D1314" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1314" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1314" s="2" t="inlineStr">
+        <is>
+          <t>331 RODRIGO MOURA REPRESENTACOES DE CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="G1314" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1314" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1314" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1314" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1314" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1314" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1314" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1314" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1314" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1314" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1314" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1315" s="2" t="n">
+        <v>565607.0</v>
+      </c>
+      <c r="C1315" s="2" t="inlineStr">
+        <is>
+          <t>43860010411</t>
+        </is>
+      </c>
+      <c r="D1315" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1315" s="2" t="inlineStr">
+        <is>
+          <t>SPC</t>
+        </is>
+      </c>
+      <c r="F1315" s="2" t="inlineStr">
+        <is>
+          <t>331 RODRIGO MOURA REPRESENTACOES DE CALCADOS LTDA</t>
+        </is>
+      </c>
+      <c r="G1315" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1315" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1315" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1315" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1315" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1315" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1315" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1315" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1315" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1315" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Q1315" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1316" s="2" t="n">
+        <v>565625.0</v>
+      </c>
+      <c r="C1316" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1316" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1316" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1316" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1316" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1316" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1316" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1316" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1316" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1316" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1316" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1316" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1316" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1316" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1316" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1317" s="2" t="n">
+        <v>565625.0</v>
+      </c>
+      <c r="C1317" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1317" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1317" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1317" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1317" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1317" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1317" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1317" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1317" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1317" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1317" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1317" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1317" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1317" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1317" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1318" s="2" t="n">
+        <v>565626.0</v>
+      </c>
+      <c r="C1318" s="2" t="inlineStr">
+        <is>
+          <t>43860000306</t>
+        </is>
+      </c>
+      <c r="D1318" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1318" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1318" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1318" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1318" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1318" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1318" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1318" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1318" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1318" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1318" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1318" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1318" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1318" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1319" s="2" t="n">
+        <v>565626.0</v>
+      </c>
+      <c r="C1319" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D1319" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1319" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1319" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1319" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1319" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1319" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1319" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1319" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1319" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1319" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1319" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1319" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1319" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1319" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1320" s="2" t="n">
+        <v>565627.0</v>
+      </c>
+      <c r="C1320" s="2" t="inlineStr">
+        <is>
+          <t>08760000007</t>
+        </is>
+      </c>
+      <c r="D1320" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1320" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1320" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1320" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1320" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1320" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1320" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1320" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1320" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1320" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1320" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1320" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1320" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1320" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1321" s="2" t="n">
+        <v>565735.0</v>
+      </c>
+      <c r="C1321" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1321" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1321" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1321" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1321" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1321" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1321" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1321" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1321" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1321" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1321" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1321" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1321" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1321" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1321" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1322" s="2" t="n">
+        <v>565735.0</v>
+      </c>
+      <c r="C1322" s="2" t="inlineStr">
+        <is>
+          <t>43860010007</t>
+        </is>
+      </c>
+      <c r="D1322" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1322" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1322" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1322" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1322" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1322" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1322" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1322" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1322" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1322" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1322" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1322" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1322" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1322" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1323" s="2" t="n">
+        <v>565736.0</v>
+      </c>
+      <c r="C1323" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1323" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1323" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1323" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1323" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1323" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1323" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1323" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1323" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1323" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1323" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1323" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1323" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1323" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1323" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1324" s="2" t="n">
+        <v>565736.0</v>
+      </c>
+      <c r="C1324" s="2" t="inlineStr">
+        <is>
+          <t>44860010007</t>
+        </is>
+      </c>
+      <c r="D1324" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1324" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1324" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1324" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1324" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1324" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1324" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1324" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1324" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1324" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1324" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1324" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1324" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1324" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1325" s="2" t="n">
+        <v>565737.0</v>
+      </c>
+      <c r="C1325" s="2" t="inlineStr">
+        <is>
+          <t>08760010007</t>
+        </is>
+      </c>
+      <c r="D1325" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1325" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1325" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1325" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1325" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1325" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1325" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1325" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1325" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1325" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1325" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1325" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1325" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1325" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1326" s="2" t="n">
+        <v>565737.0</v>
+      </c>
+      <c r="C1326" s="2" t="inlineStr">
+        <is>
+          <t>08760014005</t>
+        </is>
+      </c>
+      <c r="D1326" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE NUDE</t>
+        </is>
+      </c>
+      <c r="E1326" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1326" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1326" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1326" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1326" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1326" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1326" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1326" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1326" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1326" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1326" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1326" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1326" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1327" s="2" t="n">
+        <v>565737.0</v>
+      </c>
+      <c r="C1327" s="2" t="inlineStr">
+        <is>
+          <t>08760020306</t>
+        </is>
+      </c>
+      <c r="D1327" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO/PINK</t>
+        </is>
+      </c>
+      <c r="E1327" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1327" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1327" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1327" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1327" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1327" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1327" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1327" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1327" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1327" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1327" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1327" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1327" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1328" s="2" t="n">
+        <v>565738.0</v>
+      </c>
+      <c r="C1328" s="2" t="inlineStr">
+        <is>
+          <t>45560000017</t>
+        </is>
+      </c>
+      <c r="D1328" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 RETRO BRANCO/ROSA</t>
+        </is>
+      </c>
+      <c r="E1328" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1328" s="2" t="inlineStr">
+        <is>
+          <t>61 EDMAR FERREIRA LIMA E CIA LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1328" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="H1328" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1328" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1328" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1328" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1328" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1328" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1328" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1328" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1328" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1328" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1329" s="2" t="n">
+        <v>565828.0</v>
+      </c>
+      <c r="C1329" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1329" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1329" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1329" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1329" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1329" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1329" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1329" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1329" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1329" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1329" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1329" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1329" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1329" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1329" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1330" s="2" t="n">
+        <v>565828.0</v>
+      </c>
+      <c r="C1330" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1330" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1330" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1330" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1330" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1330" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1330" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1330" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1330" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1330" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1330" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1330" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1330" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1330" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1330" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1331" s="2" t="n">
+        <v>565841.0</v>
+      </c>
+      <c r="C1331" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1331" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1331" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1331" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1331" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1331" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1331" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1331" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1331" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1331" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1331" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1331" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1331" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1331" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1331" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1332" s="2" t="n">
+        <v>565841.0</v>
+      </c>
+      <c r="C1332" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1332" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1332" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1332" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1332" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1332" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1332" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1332" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1332" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1332" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1332" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1332" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1332" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1332" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1332" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1333" s="2" t="n">
+        <v>565846.0</v>
+      </c>
+      <c r="C1333" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1333" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1333" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1333" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1333" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1333" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1333" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1333" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1333" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1333" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1333" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1333" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1333" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1333" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1333" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1334" s="2" t="n">
+        <v>565846.0</v>
+      </c>
+      <c r="C1334" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1334" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1334" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1334" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1334" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1334" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1334" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1334" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1334" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1334" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1334" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1334" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1334" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1334" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1334" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1335" s="2" t="n">
+        <v>565850.0</v>
+      </c>
+      <c r="C1335" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1335" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1335" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1335" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1335" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1335" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1335" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1335" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1335" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1335" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1335" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1335" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1335" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1335" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1335" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1336" s="2" t="n">
+        <v>565850.0</v>
+      </c>
+      <c r="C1336" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1336" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1336" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1336" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1336" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1336" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1336" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1336" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1336" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1336" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1336" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1336" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1336" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1336" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1336" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1337" s="2" t="n">
+        <v>565854.0</v>
+      </c>
+      <c r="C1337" s="2" t="inlineStr">
+        <is>
+          <t>44860000007</t>
+        </is>
+      </c>
+      <c r="D1337" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1337" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1337" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1337" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1337" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1337" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1337" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1337" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1337" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1337" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1337" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1337" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1337" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1337" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1338" s="2" t="n">
+        <v>565854.0</v>
+      </c>
+      <c r="C1338" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1338" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1338" s="2" t="inlineStr">
+        <is>
+          <t>REM</t>
+        </is>
+      </c>
+      <c r="F1338" s="2" t="inlineStr">
+        <is>
+          <t>371 TSTH 1 990 SAMUEL REPRESENTANTE COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="G1338" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1338" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1338" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1338" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1338" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1338" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1338" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1338" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1338" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1338" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1338" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1339" s="2" t="n">
+        <v>565856.0</v>
+      </c>
+      <c r="C1339" s="2" t="inlineStr">
+        <is>
+          <t>08760010007</t>
+        </is>
+      </c>
+      <c r="D1339" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1339" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1339" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1339" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1339" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1339" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1339" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1339" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1339" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1339" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1339" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1339" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1339" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q1339" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1340" s="2" t="n">
+        <v>565856.0</v>
+      </c>
+      <c r="C1340" s="2" t="inlineStr">
+        <is>
+          <t>08760014005</t>
+        </is>
+      </c>
+      <c r="D1340" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE NUDE</t>
+        </is>
+      </c>
+      <c r="E1340" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1340" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1340" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1340" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1340" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1340" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1340" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1340" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1340" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1340" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1340" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1340" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1340" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1341" s="2" t="n">
+        <v>565860.0</v>
+      </c>
+      <c r="C1341" s="2" t="inlineStr">
+        <is>
+          <t>44860004005</t>
+        </is>
+      </c>
+      <c r="D1341" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1341" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1341" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1341" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1341" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1341" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1341" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1341" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1341" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1341" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1341" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="O1341" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1341" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1341" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1342" s="2" t="n">
+        <v>565860.0</v>
+      </c>
+      <c r="C1342" s="2" t="inlineStr">
+        <is>
+          <t>44860010411</t>
+        </is>
+      </c>
+      <c r="D1342" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC PRETO/PRETO</t>
+        </is>
+      </c>
+      <c r="E1342" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE</t>
+        </is>
+      </c>
+      <c r="F1342" s="2" t="inlineStr">
+        <is>
+          <t>317 GESTTO BRANDS REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="G1342" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1342" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1342" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1342" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1342" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L1342" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M1342" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="N1342" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1342" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1342" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1342" s="2" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1343" s="2" t="n">
+        <v>565902.0</v>
+      </c>
+      <c r="C1343" s="2" t="inlineStr">
+        <is>
+          <t>44860014005</t>
+        </is>
+      </c>
+      <c r="D1343" s="2" t="inlineStr">
+        <is>
+          <t>TENIS K360 ESTILO RESPITEC NUDE</t>
+        </is>
+      </c>
+      <c r="E1343" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1343" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1343" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="H1343" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1343" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1343" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1343" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1343" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1343" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1343" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1343" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1343" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1343" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1344" s="2" t="n">
+        <v>565903.0</v>
+      </c>
+      <c r="C1344" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1344" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1344" s="2" t="inlineStr">
+        <is>
+          <t>NORTE/NORDESTE</t>
+        </is>
+      </c>
+      <c r="F1344" s="2" t="inlineStr">
+        <is>
+          <t>53 ODELON P. DA SILVA REPRESENTAÇOES LTDA ME</t>
+        </is>
+      </c>
+      <c r="G1344" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1344" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1344" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1344" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K1344" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1344" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1344" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1344" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1344" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P1344" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1344" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1345" s="2" t="n">
+        <v>565933.0</v>
+      </c>
+      <c r="C1345" s="2" t="inlineStr">
+        <is>
+          <t>43860000007</t>
+        </is>
+      </c>
+      <c r="D1345" s="2" t="inlineStr">
+        <is>
+          <t>T.KIDY SUPER CONFORTO RESPITEC PRETO</t>
+        </is>
+      </c>
+      <c r="E1345" s="2" t="inlineStr">
+        <is>
+          <t>MS/MT</t>
+        </is>
+      </c>
+      <c r="F1345" s="2" t="inlineStr">
+        <is>
+          <t>266 LORAN DA SILVA SANTOS REPRESENTAÇÕES EIRELI</t>
+        </is>
+      </c>
+      <c r="G1345" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="H1345" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1345" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1345" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1345" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1345" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1345" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1345" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1345" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1345" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1345" s="2" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026</t>
+        </is>
+      </c>
+      <c r="B1346" s="2" t="n">
+        <v>565934.0</v>
+      </c>
+      <c r="C1346" s="2" t="inlineStr">
+        <is>
+          <t>08760000007</t>
+        </is>
+      </c>
+      <c r="D1346" s="2" t="inlineStr">
+        <is>
+          <t>TENIS KIDY USEFULL COLLEGE PRETO</t>
+        </is>
+      </c>
+      <c r="E1346" s="2" t="inlineStr">
+        <is>
+          <t>MS/MT</t>
+        </is>
+      </c>
+      <c r="F1346" s="2" t="inlineStr">
+        <is>
+          <t>266 LORAN DA SILVA SANTOS REPRESENTAÇÕES EIRELI</t>
+        </is>
+      </c>
+      <c r="G1346" s="2" t="inlineStr">
+        <is>
+          <t>087</t>
+        </is>
+      </c>
+      <c r="H1346" s="2" t="inlineStr">
+        <is>
+          <t>ABERTO</t>
+        </is>
+      </c>
+      <c r="I1346" s="2" t="inlineStr">
+        <is>
+          <t>PRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="J1346" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K1346" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="L1346" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="M1346" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="N1346" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="O1346" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P1346" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="Q1346" s="2" t="n">
         <v>12.0</v>
       </c>
     </row>
